--- a/docs/compliance/RBM_DFI_Directive_2018_Compliance_Audit.xlsx
+++ b/docs/compliance/RBM_DFI_Directive_2018_Compliance_Audit.xlsx
@@ -1813,7 +1813,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-08 20:53:36 from maiic_ifrs9_bootstrap. The PASS/FAIL in column E is a formula on columns B and C, so it recomputes if a figure is typed over.</t>
+          <t>Generated 2026-10-08 21:18:15 from maiic_ifrs9_bootstrap. The PASS/FAIL in column E is a formula on columns B and C, so it recomputes if a figure is typed over.</t>
         </is>
       </c>
     </row>

--- a/docs/compliance/RBM_DFI_Directive_2018_Compliance_Audit.xlsx
+++ b/docs/compliance/RBM_DFI_Directive_2018_Compliance_Audit.xlsx
@@ -1535,25 +1535,29 @@
       </c>
       <c r="E17" s="22" t="inlineStr">
         <is>
-          <t>The RBM Classification and IFRS 9 vs RBM reports render and export; the prescribed return form is not reproduced line for line.</t>
+          <t>RbmReturnService fills the return in the directive's own order from the system: A the facilities by class and term under the directive's day bands, B the minimum provision per class against the IFRS 9 allowance with the higher of the two, C interest in suspense on non-performing facilities, D restructured facilities (awaiting the Reschedule Report), E the security on the register; on the screen with the CSV. The layout is provisional: the prescribed form is MAIIC Risk's and is not in the repository.</t>
         </is>
       </c>
       <c r="F17" s="22" t="inlineStr"/>
       <c r="G17" s="22" t="inlineStr">
         <is>
-          <t>Partially done: the figures exist; the form is to be mapped.</t>
+          <t>Partially done: every line is filled; the form's own order and wording are applied when Risk supplies it.</t>
         </is>
       </c>
       <c r="H17" s="22" t="inlineStr">
         <is>
-          <t>Risk &amp; Regulatory, RBM Classification: /ifrs9-reports/rbm-classification; IFRS 9 vs RBM: /ifrs9-reports/ifrs9-vs-rbm</t>
+          <t>Risk &amp; Regulatory, RBM Return (provisional): /rbm-return; Risk &amp; Regulatory, RBM Classification: /ifrs9-reports/rbm-classification; IFRS 9 vs RBM: /ifrs9-reports/ifrs9-vs-rbm</t>
         </is>
       </c>
       <c r="I17" s="22" t="inlineStr"/>
-      <c r="J17" s="22" t="inlineStr"/>
+      <c r="J17" s="22" t="inlineStr">
+        <is>
+          <t>dpd_basis</t>
+        </is>
+      </c>
       <c r="K17" s="22" t="inlineStr">
         <is>
-          <t>Tests\Feature\Eir\StagingServiceTest</t>
+          <t>Tests\Feature\Rbm\RbmReturnServiceTest</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1613,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1733,22 +1737,22 @@
       </c>
       <c r="C6" s="22" t="inlineStr">
         <is>
-          <t>The prescribed return form is not mapped</t>
+          <t>The prescribed return form is not in the repository</t>
         </is>
       </c>
       <c r="D6" s="22" t="inlineStr">
         <is>
-          <t>The reports carry the figures; the Reserve Bank's form is not reproduced line for line.</t>
+          <t>The provisional return fills every line the directive asks for, in the directive's order; the Reserve Bank's own form (its schedule number, order and wording) has not been supplied.</t>
         </is>
       </c>
       <c r="E6" s="22" t="inlineStr">
         <is>
-          <t>The return is prepared outside the system.</t>
+          <t>The return is still transcribed into the Bank's form by hand.</t>
         </is>
       </c>
       <c r="F6" s="22" t="inlineStr">
         <is>
-          <t>MAIIC Risk supplies the current form; the mapping is added to the IFRS 9 vs RBM report.</t>
+          <t>MAIIC Risk supplies the current form (the Excel or PDF sent to the Bank); the provisional layout is re-ordered and re-worded to it line for line; the figures stay as they are.</t>
         </is>
       </c>
       <c r="G6" s="22" t="inlineStr">
@@ -1757,6 +1761,48 @@
         </is>
       </c>
       <c r="H6" s="22" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="22" t="inlineStr">
+        <is>
+          <t>F3</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>9 to 11</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>The RBM Classification report's day bands differ from the directive's</t>
+        </is>
+      </c>
+      <c r="D7" s="22" t="inlineStr">
+        <is>
+          <t>The older RBM Classification report classifies every facility on one ladder (90, 180, 365 days); the directive classifies by term (90/180/360 for short-term, 180/360/720 for medium and long). The provisional return applies the directive's bands.</t>
+        </is>
+      </c>
+      <c r="E7" s="22" t="inlineStr">
+        <is>
+          <t>The two screens can show different classes for the same medium-term facility.</t>
+        </is>
+      </c>
+      <c r="F7" s="22" t="inlineStr">
+        <is>
+          <t>Align the RBM Classification report to the directive's bands by term (or retire it in favour of the return).</t>
+        </is>
+      </c>
+      <c r="G7" s="22" t="inlineStr">
+        <is>
+          <t>Dupleix</t>
+        </is>
+      </c>
+      <c r="H7" s="22" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -1764,7 +1810,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="H5:H6" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H5:H7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Open,In progress,Closed,Deferred"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1813,7 +1859,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-08 21:18:15 from maiic_ifrs9_bootstrap. The PASS/FAIL in column E is a formula on columns B and C, so it recomputes if a figure is typed over.</t>
+          <t>Generated 2026-10-08 21:50:42 from maiic_ifrs9_bootstrap. The PASS/FAIL in column E is a formula on columns B and C, so it recomputes if a figure is typed over.</t>
         </is>
       </c>
     </row>

--- a/docs/compliance/RBM_DFI_Directive_2018_Compliance_Audit.xlsx
+++ b/docs/compliance/RBM_DFI_Directive_2018_Compliance_Audit.xlsx
@@ -1224,7 +1224,7 @@
       </c>
       <c r="E8" s="22" t="inlineStr">
         <is>
-          <t>The RBM Classification report classifies each loan from the days past due the build counts from the oldest overdue instalment, with the bucket ageing beside it; the IFRS 9 stage is mapped to the RBM class in the IFRS 9 vs RBM report.</t>
+          <t>The RBM Classification report classifies each loan from the days past due the build counts from the oldest overdue instalment, under the directive's bands by term of facility (the same bands as the RBM Return, proven to agree at every band edge); the arrears ageing shows the class beside each day band; the IFRS 9 stage is mapped to the RBM class in the IFRS 9 vs RBM report.</t>
         </is>
       </c>
       <c r="F8" s="22" t="inlineStr"/>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="K8" s="22" t="inlineStr">
         <is>
-          <t>Tests\Feature\Eir\StagingServiceTest</t>
+          <t>Tests\Feature\Rbm\RbmReturnServiceTest::test_the_rbm_classification_report_agrees_with_the_return_on_every_loan</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E10" s="22" t="inlineStr">
         <is>
-          <t>The RBM Classification report applies the day bands; the loan book's buckets end at 271 to 360 days and the build counts days from the overdue date without a ceiling, so the doubtful and loss bands are classified from the day count; the qualitative 'recovery not expected' flag is the write-off policy MAIIC has not stated.</t>
+          <t>The RBM Classification report and the RBM Return apply the doubtful and loss bands by term (181/361 days short-term, 361/721 otherwise); the loan book's buckets end at 271 to 360 days and the build counts days from the overdue date without a ceiling, so the bands are classified from the day count; the qualitative 'recovery not expected' flag is the write-off policy MAIIC has not stated.</t>
         </is>
       </c>
       <c r="F10" s="22" t="inlineStr"/>
@@ -1344,7 +1344,7 @@
       <c r="J10" s="22" t="inlineStr"/>
       <c r="K10" s="22" t="inlineStr">
         <is>
-          <t>Tests\Feature\Eir\StagingServiceTest</t>
+          <t>Tests\Feature\Rbm\RbmReturnServiceTest</t>
         </is>
       </c>
     </row>
@@ -1779,22 +1779,22 @@
       </c>
       <c r="C7" s="22" t="inlineStr">
         <is>
-          <t>The RBM Classification report's day bands differ from the directive's</t>
+          <t>The RBM Classification report's day bands differed from the directive's</t>
         </is>
       </c>
       <c r="D7" s="22" t="inlineStr">
         <is>
-          <t>The older RBM Classification report classifies every facility on one ladder (90, 180, 365 days); the directive classifies by term (90/180/360 for short-term, 180/360/720 for medium and long). The provisional return applies the directive's bands.</t>
+          <t>The older RBM Classification report classified every facility on one ladder (90, 180, 365 days) with 1 percent on pass and special mention; the directive classifies by term (90/180/360 for short-term, 180/360/720 for medium and long) with 0 and 5 percent. Resolved 9 October 2026: the report, the provision comparison and the arrears ageing now classify by the directive's bands by term and rates, from the same rule as the return; a test proves the two agree at every band edge on both terms.</t>
         </is>
       </c>
       <c r="E7" s="22" t="inlineStr">
         <is>
-          <t>The two screens can show different classes for the same medium-term facility.</t>
+          <t>None remaining: the two screens show one class for every facility.</t>
         </is>
       </c>
       <c r="F7" s="22" t="inlineStr">
         <is>
-          <t>Align the RBM Classification report to the directive's bands by term (or retire it in favour of the return).</t>
+          <t>Done.</t>
         </is>
       </c>
       <c r="G7" s="22" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="H7" s="22" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-08 21:50:42 from maiic_ifrs9_bootstrap. The PASS/FAIL in column E is a formula on columns B and C, so it recomputes if a figure is typed over.</t>
+          <t>Generated 2026-10-08 22:00:02 from maiic_ifrs9_bootstrap. The PASS/FAIL in column E is a formula on columns B and C, so it recomputes if a figure is typed over.</t>
         </is>
       </c>
     </row>

--- a/docs/compliance/RBM_DFI_Directive_2018_Compliance_Audit.xlsx
+++ b/docs/compliance/RBM_DFI_Directive_2018_Compliance_Audit.xlsx
@@ -1316,7 +1316,7 @@
       </c>
       <c r="C10" s="22" t="inlineStr">
         <is>
-          <t>Doubtful from 181 (short-term) or 361 days (medium and long term); loss from 361 or 721 days, or where recovery is not expected.</t>
+          <t>Doubtful from 181 (short-term) or 366 days (medium and long term); loss beyond 365 or 746 days, or where recovery is not expected.</t>
         </is>
       </c>
       <c r="D10" s="23" t="inlineStr">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E10" s="22" t="inlineStr">
         <is>
-          <t>The RBM Classification report and the RBM Return apply the doubtful and loss bands by term (181/361 days short-term, 361/721 otherwise); the loan book's buckets end at 271 to 360 days and the build counts days from the overdue date without a ceiling, so the bands are classified from the day count; the qualitative 'recovery not expected' flag is the write-off policy MAIIC has not stated.</t>
+          <t>The RBM Classification report and the RBM Return apply the doubtful and loss bands by term from section 10 of the Gazette (181/366 days short-term, 366/747 otherwise); the loan book's buckets end at 271 to 360 days and the build counts days from the overdue date without a ceiling, so the bands are classified from the day count; the qualitative 'recovery not expected' flag is the write-off policy MAIIC has not stated.</t>
         </is>
       </c>
       <c r="F10" s="22" t="inlineStr"/>
@@ -1784,12 +1784,12 @@
       </c>
       <c r="D7" s="22" t="inlineStr">
         <is>
-          <t>The older RBM Classification report classified every facility on one ladder (90, 180, 365 days) with 1 percent on pass and special mention; the directive classifies by term (90/180/360 for short-term, 180/360/720 for medium and long) with 0 and 5 percent. Resolved 9 October 2026: the report, the provision comparison and the arrears ageing now classify by the directive's bands by term and rates, from the same rule as the return; a test proves the two agree at every band edge on both terms.</t>
+          <t>The older RBM Classification report classified every facility on one ladder (90, 180, 365 days) with 1 percent on pass and special mention. Resolved in two steps: on 9 October 2026 the report, the provision comparison and the arrears ageing were put on one rule with the RBM Return; the system audit of the same day then found that rule itself carried wrong medium- and long-term bands (30/180/360/720, from a note carried between sessions) and both were corrected to the Gazette's section 10: short-term 30/90/180/365, medium and long 90/180/365/746, with a test at every boundary on both terms.</t>
         </is>
       </c>
       <c r="E7" s="22" t="inlineStr">
         <is>
-          <t>None remaining: the two screens show one class for every facility.</t>
+          <t>None remaining: both screens classify by the Gazette's bands.</t>
         </is>
       </c>
       <c r="F7" s="22" t="inlineStr">
@@ -1859,7 +1859,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-08 22:00:02 from maiic_ifrs9_bootstrap. The PASS/FAIL in column E is a formula on columns B and C, so it recomputes if a figure is typed over.</t>
+          <t>Generated 2026-10-09 00:03:49 from maiic_ifrs9_bootstrap. The PASS/FAIL in column E is a formula on columns B and C, so it recomputes if a figure is typed over.</t>
         </is>
       </c>
     </row>

--- a/docs/compliance/RBM_DFI_Directive_2018_Compliance_Audit.xlsx
+++ b/docs/compliance/RBM_DFI_Directive_2018_Compliance_Audit.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Baselines" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Audit'!$A$4:$K$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Audit'!$A$4:$K$26</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Audit'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Findings'!$4:$4</definedName>
   </definedNames>
@@ -604,7 +604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="C10" s="13">
-        <f>COUNTA(Audit!$A$5:$A$17)-5</f>
+        <f>COUNTA(Audit!$A$5:$A$26)-3</f>
         <v/>
       </c>
     </row>
@@ -794,19 +794,19 @@
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>PART III - CLASSIFICATION</t>
+          <t>PART III - REQUIREMENTS</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="16" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4(b)(vi), 4(b)(x)</t>
         </is>
       </c>
       <c r="B17" s="17" t="inlineStr">
         <is>
-          <t>Classification of credit facilities</t>
+          <t>Board-approved written policies: write-offs of loss facilities; restructuring</t>
         </is>
       </c>
       <c r="C17" s="16">
@@ -822,12 +822,12 @@
     <row r="18">
       <c r="A18" s="16" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5(1)(b)</t>
         </is>
       </c>
       <c r="B18" s="17" t="inlineStr">
         <is>
-          <t>Non-performing: substandard from 91 days (short-term) or 181 days (medium and long term)</t>
+          <t>Written valuation methods for collateral</t>
         </is>
       </c>
       <c r="C18" s="16">
@@ -843,12 +843,12 @@
     <row r="19">
       <c r="A19" s="16" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B19" s="17" t="inlineStr">
         <is>
-          <t>Doubtful and loss</t>
+          <t>Classification of credit facilities</t>
         </is>
       </c>
       <c r="C19" s="16">
@@ -862,21 +862,35 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="15" t="inlineStr">
-        <is>
-          <t>PART IV - PROVISIONING</t>
+      <c r="A20" s="16" t="inlineStr">
+        <is>
+          <t>11(1), 11(2)</t>
+        </is>
+      </c>
+      <c r="B20" s="17" t="inlineStr">
+        <is>
+          <t>Quarterly review of all facilities; prompt reclassification</t>
+        </is>
+      </c>
+      <c r="C20" s="16">
+        <f>Audit!D11</f>
+        <v/>
+      </c>
+      <c r="D20" s="17" t="inlineStr">
+        <is>
+          <t>Audit row 11</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="16" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11(3)</t>
         </is>
       </c>
       <c r="B21" s="17" t="inlineStr">
         <is>
-          <t>Minimum provisions by class</t>
+          <t>Review each large exposure individually</t>
         </is>
       </c>
       <c r="C21" s="16">
@@ -892,12 +906,12 @@
     <row r="22">
       <c r="A22" s="16" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B22" s="17" t="inlineStr">
         <is>
-          <t>Non-accrual of interest</t>
+          <t>Write off loss facilities in the following quarter</t>
         </is>
       </c>
       <c r="C22" s="16">
@@ -911,21 +925,35 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="15" t="inlineStr">
-        <is>
-          <t>PART V - RESTRUCTURING</t>
+      <c r="A23" s="16" t="inlineStr">
+        <is>
+          <t>13(1)</t>
+        </is>
+      </c>
+      <c r="B23" s="17" t="inlineStr">
+        <is>
+          <t>Non-accrual: cease accrual, reverse uncollected interest, recognise interest only when received in cash</t>
+        </is>
+      </c>
+      <c r="C23" s="16">
+        <f>Audit!D14</f>
+        <v/>
+      </c>
+      <c r="D23" s="17" t="inlineStr">
+        <is>
+          <t>Audit row 14</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="16" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13(2)</t>
         </is>
       </c>
       <c r="B24" s="17" t="inlineStr">
         <is>
-          <t>Restructured facilities</t>
+          <t>Non-accrual regardless of collateral</t>
         </is>
       </c>
       <c r="C24" s="16">
@@ -939,21 +967,35 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="15" t="inlineStr">
-        <is>
-          <t>PART VI - REPORTING</t>
+      <c r="A25" s="16" t="inlineStr">
+        <is>
+          <t>13(3)</t>
+        </is>
+      </c>
+      <c r="B25" s="17" t="inlineStr">
+        <is>
+          <t>Restore to accrual only when all arrears are paid</t>
+        </is>
+      </c>
+      <c r="C25" s="16">
+        <f>Audit!D16</f>
+        <v/>
+      </c>
+      <c r="D25" s="17" t="inlineStr">
+        <is>
+          <t>Audit row 16</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="16" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>14 and Schedule</t>
         </is>
       </c>
       <c r="B26" s="17" t="inlineStr">
         <is>
-          <t>Returns to the Reserve Bank</t>
+          <t>Minimum provisions by class</t>
         </is>
       </c>
       <c r="C26" s="16">
@@ -966,36 +1008,209 @@
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" s="16" t="inlineStr">
+        <is>
+          <t>15(1)</t>
+        </is>
+      </c>
+      <c r="B27" s="17" t="inlineStr">
+        <is>
+          <t>Excess of the regulatory provision over IFRS to a loan loss reserve</t>
+        </is>
+      </c>
+      <c r="C27" s="16">
+        <f>Audit!D18</f>
+        <v/>
+      </c>
+      <c r="D27" s="17" t="inlineStr">
+        <is>
+          <t>Audit row 18</t>
+        </is>
+      </c>
+    </row>
     <row r="28">
-      <c r="A28" s="18" t="inlineStr">
+      <c r="A28" s="16" t="inlineStr">
+        <is>
+          <t>15(2), 15(4)</t>
+        </is>
+      </c>
+      <c r="B28" s="17" t="inlineStr">
+        <is>
+          <t>The reserve is not capital; released only after recoveries or with the Registrar's approval</t>
+        </is>
+      </c>
+      <c r="C28" s="16">
+        <f>Audit!D19</f>
+        <v/>
+      </c>
+      <c r="D28" s="17" t="inlineStr">
+        <is>
+          <t>Audit row 19</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="16" t="inlineStr">
+        <is>
+          <t>15(3)</t>
+        </is>
+      </c>
+      <c r="B29" s="17" t="inlineStr">
+        <is>
+          <t>Report loan loss reserves on the call report as prescribed</t>
+        </is>
+      </c>
+      <c r="C29" s="16">
+        <f>Audit!D20</f>
+        <v/>
+      </c>
+      <c r="D29" s="17" t="inlineStr">
+        <is>
+          <t>Audit row 20</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="16" t="inlineStr">
+        <is>
+          <t>16(1)</t>
+        </is>
+      </c>
+      <c r="B30" s="17" t="inlineStr">
+        <is>
+          <t>No restructure, renegotiation, roll-over or modification without Board approval</t>
+        </is>
+      </c>
+      <c r="C30" s="16">
+        <f>Audit!D21</f>
+        <v/>
+      </c>
+      <c r="D30" s="17" t="inlineStr">
+        <is>
+          <t>Audit row 21</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="16" t="inlineStr">
+        <is>
+          <t>16(2)</t>
+        </is>
+      </c>
+      <c r="B31" s="17" t="inlineStr">
+        <is>
+          <t>Single borrower or group limit of 25 percent of core capital</t>
+        </is>
+      </c>
+      <c r="C31" s="16">
+        <f>Audit!D22</f>
+        <v/>
+      </c>
+      <c r="D31" s="17" t="inlineStr">
+        <is>
+          <t>Audit row 22</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="16" t="inlineStr">
+        <is>
+          <t>16(3)</t>
+        </is>
+      </c>
+      <c r="B32" s="17" t="inlineStr">
+        <is>
+          <t>No overdraft facilities</t>
+        </is>
+      </c>
+      <c r="C32" s="16">
+        <f>Audit!D23</f>
+        <v/>
+      </c>
+      <c r="D32" s="17" t="inlineStr">
+        <is>
+          <t>Audit row 23</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="16" t="inlineStr">
+        <is>
+          <t>3 to 9</t>
+        </is>
+      </c>
+      <c r="B33" s="17" t="inlineStr">
+        <is>
+          <t>Objectives; Board and executive duties; lending criteria; funding records; internal audit; independent risk function</t>
+        </is>
+      </c>
+      <c r="C33" s="16">
+        <f>Audit!D24</f>
+        <v/>
+      </c>
+      <c r="D33" s="17" t="inlineStr">
+        <is>
+          <t>Audit row 24</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="15" t="inlineStr">
+        <is>
+          <t>PART IV - ENFORCEMENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="16" t="inlineStr">
+        <is>
+          <t>17, 18</t>
+        </is>
+      </c>
+      <c r="B35" s="17" t="inlineStr">
+        <is>
+          <t>Monetary and administrative penalties; auditor qualification</t>
+        </is>
+      </c>
+      <c r="C35" s="16">
+        <f>Audit!D26</f>
+        <v/>
+      </c>
+      <c r="D35" s="17" t="inlineStr">
+        <is>
+          <t>Audit row 26</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="18" t="inlineStr">
         <is>
           <t>Findings that need a decision or a fix: see the 'Findings' sheet</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="18" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="18" t="inlineStr">
         <is>
           <t>The acceptance ties read from the system: see the 'Baselines' sheet</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="19" t="inlineStr">
-        <is>
-          <t>Source: docs/regulatory/RBM Financial Services (Credit Risk Management for DFIs) Directive 2018 pp42-47.pdf. Spec v4 section 3.6, decision D31; the O13 rebuttal paper of 8 October 2026.</t>
+    <row r="39">
+      <c r="A39" s="19" t="inlineStr">
+        <is>
+          <t>Source: docs/regulatory/RBM Financial Services (Credit Risk Management for DFIs) Directive 2018 pp42-47.pdf (Gazette 13 July 2018, pages 680 to 685). Spec v4 section 3.6, decision D31; the O13 rebuttal paper of 8 October 2026.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A23:D23"/>
-    <mergeCell ref="A20:D20"/>
-    <mergeCell ref="A25:D25"/>
+  <mergeCells count="3">
     <mergeCell ref="A16:D16"/>
     <mergeCell ref="A14:D14"/>
+    <mergeCell ref="A34:D34"/>
   </mergeCells>
-  <conditionalFormatting sqref="C14:C27">
+  <conditionalFormatting sqref="C14:C36">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$C14="Done"</formula>
     </cfRule>
@@ -1015,22 +1230,44 @@
   <hyperlinks>
     <hyperlink ref="B15" location="'Audit'!A6" display="Definitions: short-, medium- and long-term facilities"/>
     <hyperlink ref="D15" location="'Audit'!A6" display="Audit row 6"/>
-    <hyperlink ref="B17" location="'Audit'!A8" display="Classification of credit facilities"/>
+    <hyperlink ref="B17" location="'Audit'!A8" display="Board-approved written policies: write-offs of loss facilities; restructuring"/>
     <hyperlink ref="D17" location="'Audit'!A8" display="Audit row 8"/>
-    <hyperlink ref="B18" location="'Audit'!A9" display="Non-performing: substandard from 91 days (short-term) or 181 days (medium and long term)"/>
+    <hyperlink ref="B18" location="'Audit'!A9" display="Written valuation methods for collateral"/>
     <hyperlink ref="D18" location="'Audit'!A9" display="Audit row 9"/>
-    <hyperlink ref="B19" location="'Audit'!A10" display="Doubtful and loss"/>
+    <hyperlink ref="B19" location="'Audit'!A10" display="Classification of credit facilities"/>
     <hyperlink ref="D19" location="'Audit'!A10" display="Audit row 10"/>
-    <hyperlink ref="B21" location="'Audit'!A12" display="Minimum provisions by class"/>
+    <hyperlink ref="B20" location="'Audit'!A11" display="Quarterly review of all facilities; prompt reclassification"/>
+    <hyperlink ref="D20" location="'Audit'!A11" display="Audit row 11"/>
+    <hyperlink ref="B21" location="'Audit'!A12" display="Review each large exposure individually"/>
     <hyperlink ref="D21" location="'Audit'!A12" display="Audit row 12"/>
-    <hyperlink ref="B22" location="'Audit'!A13" display="Non-accrual of interest"/>
+    <hyperlink ref="B22" location="'Audit'!A13" display="Write off loss facilities in the following quarter"/>
     <hyperlink ref="D22" location="'Audit'!A13" display="Audit row 13"/>
-    <hyperlink ref="B24" location="'Audit'!A15" display="Restructured facilities"/>
+    <hyperlink ref="B23" location="'Audit'!A14" display="Non-accrual: cease accrual, reverse uncollected interest, recognise interest only when received in cash"/>
+    <hyperlink ref="D23" location="'Audit'!A14" display="Audit row 14"/>
+    <hyperlink ref="B24" location="'Audit'!A15" display="Non-accrual regardless of collateral"/>
     <hyperlink ref="D24" location="'Audit'!A15" display="Audit row 15"/>
-    <hyperlink ref="B26" location="'Audit'!A17" display="Returns to the Reserve Bank"/>
+    <hyperlink ref="B25" location="'Audit'!A16" display="Restore to accrual only when all arrears are paid"/>
+    <hyperlink ref="D25" location="'Audit'!A16" display="Audit row 16"/>
+    <hyperlink ref="B26" location="'Audit'!A17" display="Minimum provisions by class"/>
     <hyperlink ref="D26" location="'Audit'!A17" display="Audit row 17"/>
-    <hyperlink ref="A28" location="'Findings'!A1" display="Findings that need a decision or a fix: see the 'Findings' sheet"/>
-    <hyperlink ref="A29" location="'Baselines'!A1" display="The acceptance ties read from the system: see the 'Baselines' sheet"/>
+    <hyperlink ref="B27" location="'Audit'!A18" display="Excess of the regulatory provision over IFRS to a loan loss reserve"/>
+    <hyperlink ref="D27" location="'Audit'!A18" display="Audit row 18"/>
+    <hyperlink ref="B28" location="'Audit'!A19" display="The reserve is not capital; released only after recoveries or with the Registrar's approval"/>
+    <hyperlink ref="D28" location="'Audit'!A19" display="Audit row 19"/>
+    <hyperlink ref="B29" location="'Audit'!A20" display="Report loan loss reserves on the call report as prescribed"/>
+    <hyperlink ref="D29" location="'Audit'!A20" display="Audit row 20"/>
+    <hyperlink ref="B30" location="'Audit'!A21" display="No restructure, renegotiation, roll-over or modification without Board approval"/>
+    <hyperlink ref="D30" location="'Audit'!A21" display="Audit row 21"/>
+    <hyperlink ref="B31" location="'Audit'!A22" display="Single borrower or group limit of 25 percent of core capital"/>
+    <hyperlink ref="D31" location="'Audit'!A22" display="Audit row 22"/>
+    <hyperlink ref="B32" location="'Audit'!A23" display="No overdraft facilities"/>
+    <hyperlink ref="D32" location="'Audit'!A23" display="Audit row 23"/>
+    <hyperlink ref="B33" location="'Audit'!A24" display="Objectives; Board and executive duties; lending criteria; funding records; internal audit; independent risk function"/>
+    <hyperlink ref="D33" location="'Audit'!A24" display="Audit row 24"/>
+    <hyperlink ref="B35" location="'Audit'!A26" display="Monetary and administrative penalties; auditor qualification"/>
+    <hyperlink ref="D35" location="'Audit'!A26" display="Audit row 26"/>
+    <hyperlink ref="A37" location="'Findings'!A1" display="Findings that need a decision or a fix: see the 'Findings' sheet"/>
+    <hyperlink ref="A38" location="'Baselines'!A1" display="The acceptance ties read from the system: see the 'Baselines' sheet"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -1044,7 +1281,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K17"/>
+  <dimension ref="A1:K26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1063,14 +1300,14 @@
     <row r="1">
       <c r="A1" s="20" t="inlineStr">
         <is>
-          <t>Financial Services (Credit Risk Management for Development Finance Institutions) Directive 2018, Reserve Bank of Malawi (Gazette 13 July 2018, No. 18A, pages 42 to 47) - compliance audit</t>
+          <t>Financial Services (Credit Risk Management for Development Finance Institutions) Directive 2018, Reserve Bank of Malawi (Gazette 13 July 2018, pages 680 to 685) - compliance audit</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="21" t="inlineStr">
         <is>
-          <t>Malawi Agricultural and Industrial Investment Company (MAIIC) - IFRS 9 EIR and ECL system - build of 8 October 2026 against specification v4. Prepared 9 October 2026 from the staging thresholds seeded per the directive, the staged loan books of July 2024 to August 2026, and the RBM Classification and IFRS 9 vs RBM reports. Reviewer: MAIIC Risk. Status definitions: see 'Contents'.</t>
+          <t>Malawi Agricultural and Industrial Investment Company (MAIIC) - IFRS 9 EIR and ECL system - build of 14 October 2026 (branch eir_revenue_recognition, commit abe140d) against specification v4. As of 14 October 2026: the code at commit abe140d (the uncommitted screen changes in the working tree do not alter any row) and the fresh bootstrap maiic_ifrs9_results2 of 13 October 2026, made before commit 216aee2, read with SELECTs only. Paragraph references re-keyed to the Gazette on 14 October 2026 (they cited 9, 11, 12, 15 and 17 for the wrong subjects). The Gazette's text layer misprints the Schedule's short-term rows, so the short-term bands are read from paragraph 10. Reviewer: MAIIC Risk. Status definitions: see 'Contents'.</t>
         </is>
       </c>
     </row>
@@ -1158,7 +1395,7 @@
       </c>
       <c r="C6" s="22" t="inlineStr">
         <is>
-          <t>A short-term facility has a repayment period of not more than 12 months; medium-term more than 12 and up to 60; long-term more than 60.</t>
+          <t>A short-term facility has a repayment period of not more than 12 months; medium-term not less than 12 and not more than 60 months; long-term more than 60 months.</t>
         </is>
       </c>
       <c r="D6" s="23" t="inlineStr">
@@ -1168,18 +1405,22 @@
       </c>
       <c r="E6" s="22" t="inlineStr">
         <is>
-          <t>The staging thresholds are keyed by facility class and the tenor in months: DEFAULT with min_tenor 0 (short-term, 91 days) and min_tenor 13 (medium and long, 181 days), each row citing the directive's section 2; the loan book carries the tenor from the loan master.</t>
-        </is>
-      </c>
-      <c r="F6" s="22" t="inlineStr"/>
+          <t>The staging thresholds are keyed by facility class and tenor in months (DEFAULT min_tenor 0: short-term; min_tenor 13: medium and long); the RBM Return and the RBM Classification report put a tenor of 12 months or less in short-term (RbmReturnService::classify, tenor &lt;= 12).</t>
+        </is>
+      </c>
+      <c r="F6" s="22" t="inlineStr">
+        <is>
+          <t>The Gazette's medium-term definition ('not less than 12 months') overlaps the short-term one at exactly 12 months; the system reads 12 months as short-term, the more prudent reading for days past due. No test pins tenor 12 against 13.</t>
+        </is>
+      </c>
       <c r="G6" s="22" t="inlineStr">
         <is>
-          <t>Compliant.</t>
+          <t>Compliant; the 12-month overlap is an interpretation MAIIC Risk should confirm.</t>
         </is>
       </c>
       <c r="H6" s="22" t="inlineStr">
         <is>
-          <t>Governance Centre, Staging &amp; SICR Rules: /stageing-rules</t>
+          <t>Settings, Staging basis: /setting?tab=staging; Reports: RBM Classification /ifrs9-reports/rbm-classification; IFRS 9 vs RBM /ifrs9-reports/ifrs9-vs-rbm</t>
         </is>
       </c>
       <c r="I6" s="22" t="inlineStr"/>
@@ -1190,342 +1431,448 @@
       </c>
       <c r="K6" s="22" t="inlineStr">
         <is>
-          <t>Tests\Feature\Eir\StagingThresholdSeederTest</t>
+          <t>Tests\Feature\Eir\StagingThresholdSeederTest::test_short_term_facilities_are_stage_3_at_91_days_as_the_directive_classifies_them; Tests\Feature\Rbm\RbmReturnServiceTest::test_the_directive_bands_by_term</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="15" t="inlineStr">
         <is>
-          <t>PART III - CLASSIFICATION</t>
+          <t>PART III - REQUIREMENTS</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="22" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4(b)(vi), 4(b)(x)</t>
         </is>
       </c>
       <c r="B8" s="22" t="inlineStr">
         <is>
-          <t>Classification of credit facilities</t>
+          <t>Board-approved written policies: write-offs of loss facilities; restructuring</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
         <is>
-          <t>Classify every facility as pass, special mention, substandard, doubtful or loss by the days in arrears and the qualitative factors.</t>
+          <t>The Board adopts and ensures implementation of a written policy covering, among other things, write-offs of loss credit facilities and restructuring of credit facilities.</t>
         </is>
       </c>
       <c r="D8" s="23" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Evidence needed from MAIIC</t>
         </is>
       </c>
       <c r="E8" s="22" t="inlineStr">
         <is>
-          <t>The RBM Classification report classifies each loan from the days past due the build counts from the oldest overdue instalment, under the directive's bands by term of facility (the same bands as the RBM Return, proven to agree at every band edge); the arrears ageing shows the class beside each day band; the IFRS 9 stage is mapped to the RBM class in the IFRS 9 vs RBM report.</t>
-        </is>
-      </c>
-      <c r="F8" s="22" t="inlineStr"/>
+          <t>The system holds the write-offs it can see: WriteOffClassifier identifies ledger write-offs (type 300; a batch whose other leg debits GL 1064; ACCOUNT CLOSURE on a status-H account) and the write-off register (eir-write-offs) records one not on the loan account, proposed by one person and approved by another. On the fresh bootstrap: 22 ledger write-offs of 60,778,466.86 and an empty register. No Board approval is recorded against either, and no restructuring policy is held.</t>
+        </is>
+      </c>
+      <c r="F8" s="22" t="inlineStr">
+        <is>
+          <t>Built 13 October 2026 (commit 220a5a6).</t>
+        </is>
+      </c>
       <c r="G8" s="22" t="inlineStr">
         <is>
-          <t>Compliant.</t>
+          <t>Evidence needed: MAIIC's Board-approved write-off and restructuring policies.</t>
         </is>
       </c>
       <c r="H8" s="22" t="inlineStr">
         <is>
-          <t>Risk &amp; Regulatory, RBM Classification: /ifrs9-reports/rbm-classification; IFRS 9 vs RBM: /ifrs9-reports/ifrs9-vs-rbm</t>
+          <t>EIR &amp; Revenue Recognition, EIR Data, Write-offs: /eir-write-offs</t>
         </is>
       </c>
       <c r="I8" s="22" t="inlineStr"/>
-      <c r="J8" s="22" t="inlineStr">
-        <is>
-          <t>dpd_basis</t>
-        </is>
-      </c>
+      <c r="J8" s="22" t="inlineStr"/>
       <c r="K8" s="22" t="inlineStr">
         <is>
-          <t>Tests\Feature\Rbm\RbmReturnServiceTest::test_the_rbm_classification_report_agrees_with_the_return_on_every_loan</t>
+          <t>Tests\Feature\Eir\WriteOffTest::test_a_register_write_off_reaches_the_engines_only_when_a_different_person_approves_it</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="22" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5(1)(b)</t>
         </is>
       </c>
       <c r="B9" s="22" t="inlineStr">
         <is>
-          <t>Non-performing: substandard from 91 days (short-term) or 181 days (medium and long term)</t>
+          <t>Written valuation methods for collateral</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
         <is>
-          <t>A facility is non-performing when principal or interest is due and unpaid for 90 days or more on a short-term facility, or 180 days or more on a medium- or long-term facility.</t>
+          <t>An executive officer shall have written valuation methods for determining the fair value of collateral and their impact on capital and earnings.</t>
         </is>
       </c>
       <c r="D9" s="23" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Evidence needed from MAIIC</t>
         </is>
       </c>
       <c r="E9" s="22" t="inlineStr">
         <is>
-          <t>Stage 3 from 91 days for a facility of 12 months or less and from 181 days otherwise; the November 2025 model's uniform 181 days and the accounting policy's 90 days are compared in spec section 3.6 and the thresholds carry the comparison as their rebuttal basis.</t>
-        </is>
-      </c>
-      <c r="F9" s="22" t="inlineStr">
-        <is>
-          <t>The LONG_TERM proposal (91 days for every class) is seeded future-dated and inactive pending CFO sign-off.</t>
-        </is>
-      </c>
+          <t>The E-Banker security register (P2_11, 185 rows) is landed; the collateral register and allocation screens exist with a checked import, but on the fresh bootstrap collateral_registers and collateral_allocations hold no rows, and the LGD engine does not read collateral.</t>
+        </is>
+      </c>
+      <c r="F9" s="22" t="inlineStr"/>
       <c r="G9" s="22" t="inlineStr">
         <is>
-          <t>Compliant.</t>
+          <t>Evidence needed from Credit: the valuation method and the valuations; the LGD link is Dupleix's (IFRS 9 impairment workbook B5.5.55).</t>
         </is>
       </c>
       <c r="H9" s="22" t="inlineStr">
         <is>
-          <t>Risk &amp; Regulatory, RBM Classification: /ifrs9-reports/rbm-classification; IFRS 9 vs RBM: /ifrs9-reports/ifrs9-vs-rbm</t>
+          <t>Collateral Management, Collateral Register: /collateral/register</t>
         </is>
       </c>
       <c r="I9" s="22" t="inlineStr"/>
-      <c r="J9" s="22" t="inlineStr">
-        <is>
-          <t>dpd_basis; staging_rebuttal</t>
-        </is>
-      </c>
-      <c r="K9" s="22" t="inlineStr">
-        <is>
-          <t>Tests\Feature\Eir\StagingServiceTest::test_the_directive_thresholds_by_tenor_class_and_the_bucket_fallback</t>
-        </is>
-      </c>
+      <c r="J9" s="22" t="inlineStr"/>
+      <c r="K9" s="22" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="22" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B10" s="22" t="inlineStr">
         <is>
-          <t>Doubtful and loss</t>
+          <t>Classification of credit facilities</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
         <is>
-          <t>Doubtful from 181 (short-term) or 366 days (medium and long term); loss beyond 365 or 746 days, or where recovery is not expected.</t>
+          <t>Classify every facility as standard, special mention, substandard, doubtful or loss: short-term at 0-30 / 31-90 / 91-180 / 181-365 / over 365 days overdue; medium and long term at 0-90 / 91-180 / 181-365 / 366-746 / over 746 days.</t>
         </is>
       </c>
       <c r="D10" s="23" t="inlineStr">
         <is>
-          <t>Partially done</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr">
         <is>
-          <t>The RBM Classification report and the RBM Return apply the doubtful and loss bands by term from section 10 of the Gazette (181/366 days short-term, 366/747 otherwise); the loan book's buckets end at 271 to 360 days and the build counts days from the overdue date without a ceiling, so the bands are classified from the day count; the qualitative 'recovery not expected' flag is the write-off policy MAIIC has not stated.</t>
-        </is>
-      </c>
-      <c r="F10" s="22" t="inlineStr"/>
+          <t>RbmReturnService::classify applies the paragraph 10 bands by term (BANDS short 30/90/180/365, long 90/180/365/746); the RBM Classification report, the provision comparison and the arrears ageing use the same rule. Days are counted from the oldest overdue instalment; since commit 216aee2 the count reads E-Banker's instalment chart in force at each month-end (InstalmentChartHistory).</t>
+        </is>
+      </c>
+      <c r="F10" s="22" t="inlineStr">
+        <is>
+          <t>Paragraph 10 makes 31-90 days 'standard' for a medium- or long-term facility; IFRS 9 Stage 2 nevertheless starts at 31 days in every class (the B5.5.11 presumption). The LONG_TERM threshold row proposing Stage 2 at 91 days for medium- and long-term facilities only (short-term stays at 31) is seeded future-dated (2099) and inactive pending CFO sign-off.</t>
+        </is>
+      </c>
       <c r="G10" s="22" t="inlineStr">
         <is>
-          <t>Partially done: the day bands are applied; the qualitative loss criterion awaits the policy.</t>
+          <t>Compliant.</t>
         </is>
       </c>
       <c r="H10" s="22" t="inlineStr">
         <is>
-          <t>Risk &amp; Regulatory, RBM Classification: /ifrs9-reports/rbm-classification; IFRS 9 vs RBM: /ifrs9-reports/ifrs9-vs-rbm</t>
+          <t>Reports: RBM Classification /ifrs9-reports/rbm-classification; IFRS 9 vs RBM /ifrs9-reports/ifrs9-vs-rbm; Reports: RBM Return (provisional) /rbm-return</t>
         </is>
       </c>
       <c r="I10" s="22" t="inlineStr"/>
-      <c r="J10" s="22" t="inlineStr"/>
+      <c r="J10" s="22" t="inlineStr">
+        <is>
+          <t>dpd_basis</t>
+        </is>
+      </c>
       <c r="K10" s="22" t="inlineStr">
         <is>
-          <t>Tests\Feature\Rbm\RbmReturnServiceTest</t>
+          <t>Tests\Feature\Rbm\RbmReturnServiceTest::test_the_directive_bands_by_term; Tests\Feature\Rbm\RbmReturnServiceTest::test_the_rbm_classification_report_agrees_with_the_return_on_every_loan</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="15" t="inlineStr">
-        <is>
-          <t>PART IV - PROVISIONING</t>
+      <c r="A11" s="22" t="inlineStr">
+        <is>
+          <t>11(1), 11(2)</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
+        <is>
+          <t>Quarterly review of all facilities; prompt reclassification</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="inlineStr">
+        <is>
+          <t>Review all credit facilities quarterly for classification and impairment; on a significant deterioration between reviews, promptly reclassify and make the provision.</t>
+        </is>
+      </c>
+      <c r="D11" s="23" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E11" s="22" t="inlineStr">
+        <is>
+          <t>The loan book is built, staged and classified every month (eir:stage for each period; the RBM Return for any period), which is more frequent than the quarter the directive asks for.</t>
+        </is>
+      </c>
+      <c r="F11" s="22" t="inlineStr">
+        <is>
+          <t>Paragraph 9(2) (the risk function's quarterly review) is a governance duty the monthly figures support.</t>
+        </is>
+      </c>
+      <c r="G11" s="22" t="inlineStr">
+        <is>
+          <t>Compliant (monthly).</t>
+        </is>
+      </c>
+      <c r="H11" s="22" t="inlineStr">
+        <is>
+          <t>Reports: RBM Return (provisional) /rbm-return; Workspace: /workspace</t>
+        </is>
+      </c>
+      <c r="I11" s="22" t="inlineStr"/>
+      <c r="J11" s="22" t="inlineStr">
+        <is>
+          <t>dpd_basis; stage3_missed_instalments</t>
+        </is>
+      </c>
+      <c r="K11" s="22" t="inlineStr">
+        <is>
+          <t>Tests\Feature\Rbm\RbmReturnServiceTest::test_the_return_fills_the_sections_from_the_book</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="22" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11(3)</t>
         </is>
       </c>
       <c r="B12" s="22" t="inlineStr">
         <is>
-          <t>Minimum provisions by class</t>
+          <t>Review each large exposure individually</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
         <is>
-          <t>Provide at least 0 percent on pass, 5 on special mention, 20 on substandard, 50 on doubtful and 100 on loss, net of eligible security.</t>
+          <t>Review each large exposure (paragraph 2: 10 percent or more of core capital, to a person or group of related parties) on an individual item basis.</t>
         </is>
       </c>
       <c r="D12" s="23" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Partially done</t>
         </is>
       </c>
       <c r="E12" s="22" t="inlineStr">
         <is>
-          <t>The IFRS 9 vs RBM report applies the five percentages to the classified book and sets the regulatory provision beside the IFRS 9 allowance; the higher of the two is the figure the regulatory return carries.</t>
+          <t>The Concentration and large exposures report lists single names over a threshold typed on the screen (default 1,000,000; Ifrs9ReportsController::concentration). The system holds neither core capital nor groups of related borrowers, so the 10 percent test is not applied.</t>
         </is>
       </c>
       <c r="F12" s="22" t="inlineStr"/>
       <c r="G12" s="22" t="inlineStr">
         <is>
-          <t>Compliant in the report; the eligible-security netting rests on the collateral register (IFRS 7 workbook F1).</t>
+          <t>Partially done: the list exists; the threshold is not the directive's.</t>
         </is>
       </c>
       <c r="H12" s="22" t="inlineStr">
         <is>
-          <t>Risk &amp; Regulatory, RBM Classification: /ifrs9-reports/rbm-classification; IFRS 9 vs RBM: /ifrs9-reports/ifrs9-vs-rbm</t>
+          <t>Reports: Concentration and large exposures /ifrs9-reports/concentration</t>
         </is>
       </c>
       <c r="I12" s="22" t="inlineStr"/>
       <c r="J12" s="22" t="inlineStr"/>
-      <c r="K12" s="22" t="inlineStr">
-        <is>
-          <t>Tests\Feature\Ecl\TimePhasedEclServiceTest</t>
-        </is>
-      </c>
+      <c r="K12" s="22" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="22" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B13" s="22" t="inlineStr">
         <is>
-          <t>Non-accrual of interest</t>
+          <t>Write off loss facilities in the following quarter</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
         <is>
-          <t>Interest on a non-performing facility is not recognised as income; it is held in suspense until received.</t>
+          <t>Write off all facilities classified as loss from the books in the quarter following the one in which the loss classification was made.</t>
         </is>
       </c>
       <c r="D13" s="23" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Outstanding</t>
         </is>
       </c>
       <c r="E13" s="22" t="inlineStr">
         <is>
-          <t>Stage 3 interest in the EIR roll-forward is on the net basis; the contractual interest E-Banker continues to post on non-performing accounts is shown beside it in the GL reconciliation, so the suspense the directive requires is the difference the system reports.</t>
+          <t>Not built: nothing records when a facility first became loss, so the age of a loss classification is unknown and no facility is flagged as due for write-off. The write-off register is not linked to the RBM Return. On the fresh bootstrap at September 2026, 10 medium- and long-term facilities of 1,511.0m are in the loss class.</t>
         </is>
       </c>
       <c r="F13" s="22" t="inlineStr">
         <is>
-          <t>The year-end re-rating of December 2025 (28 postings) is explained in spec section 3.4.</t>
+          <t>Figures from the fresh bootstrap maiic_ifrs9_results2 (13 October 2026, before commit 216aee2), main book (the six MAIIC and FInES loan GLs) at September 2026.</t>
         </is>
       </c>
       <c r="G13" s="22" t="inlineStr">
         <is>
-          <t>Compliant; the suspense is reported, and the posting practice is Finance's to align.</t>
+          <t>Outstanding (Dupleix): a loss-since date and a due-for-write-off flag on the Return.</t>
         </is>
       </c>
       <c r="H13" s="22" t="inlineStr">
         <is>
-          <t>Report Hub, GL Reconciliation: /eir-reconciliation</t>
+          <t>Reports: RBM Return (provisional) /rbm-return; /eir-write-offs</t>
         </is>
       </c>
       <c r="I13" s="22" t="inlineStr"/>
-      <c r="J13" s="22" t="inlineStr">
+      <c r="J13" s="22" t="inlineStr"/>
+      <c r="K13" s="22" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="22" t="inlineStr">
+        <is>
+          <t>13(1)</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="inlineStr">
+        <is>
+          <t>Non-accrual: cease accrual, reverse uncollected interest, recognise interest only when received in cash</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="inlineStr">
+        <is>
+          <t>Place all non-performing facilities on non-accrual: cease accruing interest in income, reverse uncollected interest previously accrued, and recognise interest only when received in cash.</t>
+        </is>
+      </c>
+      <c r="D14" s="23" t="inlineStr">
+        <is>
+          <t>Partially done</t>
+        </is>
+      </c>
+      <c r="E14" s="22" t="inlineStr">
+        <is>
+          <t>Section C of the RBM Return reports, for the non-performing facilities, one period's contractual interest posted by E-Banker less the EIR interest recognised on the net basis. That is not the directive's measure: it is not cumulative, it is not on the cash basis (interest received), and GL 1320 (interest in suspense) is read nowhere. Under IFRS 9 the EIR engine recognises Stage 3 interest on the net carrying amount (5.4.1(b)), which is not the directive's cash basis either.</t>
+        </is>
+      </c>
+      <c r="F14" s="22" t="inlineStr"/>
+      <c r="G14" s="22" t="inlineStr">
+        <is>
+          <t>Partially done: the gap between the posted and the recognised interest is shown; the directive's suspense balance is not computed or tied to GL 1320.</t>
+        </is>
+      </c>
+      <c r="H14" s="22" t="inlineStr">
+        <is>
+          <t>Reports: RBM Return (provisional) /rbm-return (section C); EIR Calculations, GL Reconciliation: /eir-reconciliation</t>
+        </is>
+      </c>
+      <c r="I14" s="22" t="inlineStr"/>
+      <c r="J14" s="22" t="inlineStr">
         <is>
           <t>stage3_interest_basis</t>
         </is>
       </c>
-      <c r="K13" s="22" t="inlineStr">
-        <is>
-          <t>Tests\Feature\Eir\EirRevenueServiceTest</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="15" t="inlineStr">
-        <is>
-          <t>PART V - RESTRUCTURING</t>
-        </is>
-      </c>
+      <c r="K14" s="22" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="22" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13(2)</t>
         </is>
       </c>
       <c r="B15" s="22" t="inlineStr">
         <is>
-          <t>Restructured facilities</t>
+          <t>Non-accrual regardless of collateral</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
         <is>
-          <t>A restructured facility keeps its classification until the borrower has performed under the new terms for a stated period.</t>
+          <t>A non-performing facility is placed on non-accrual whatever collateral is held against it.</t>
         </is>
       </c>
       <c r="D15" s="23" t="inlineStr">
         <is>
-          <t>Evidence needed from MAIIC</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E15" s="22" t="inlineStr">
         <is>
-          <t>The restructured-loan register and E-Banker's Reschedule Report are awaited from the vendor; the loan's status history (P3_13) is landed.</t>
+          <t>The classification reads only the days overdue and the term (RbmReturnService::classify takes no collateral), so security never keeps a facility out of the non-performing classes.</t>
         </is>
       </c>
       <c r="F15" s="22" t="inlineStr"/>
       <c r="G15" s="22" t="inlineStr">
         <is>
-          <t>Evidence needed from the vendor.</t>
+          <t>Compliant.</t>
         </is>
       </c>
       <c r="H15" s="22" t="inlineStr">
         <is>
-          <t>Data Foundation, E-Banker Feed: /eir-feed</t>
+          <t>Reports: RBM Return (provisional) /rbm-return</t>
         </is>
       </c>
       <c r="I15" s="22" t="inlineStr"/>
-      <c r="J15" s="22" t="inlineStr">
-        <is>
-          <t>rate_change_classification</t>
-        </is>
-      </c>
-      <c r="K15" s="22" t="inlineStr"/>
+      <c r="J15" s="22" t="inlineStr"/>
+      <c r="K15" s="22" t="inlineStr">
+        <is>
+          <t>Tests\Feature\Rbm\RbmReturnServiceTest::test_the_directive_bands_by_term</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="15" t="inlineStr">
-        <is>
-          <t>PART VI - REPORTING</t>
-        </is>
-      </c>
+      <c r="A16" s="22" t="inlineStr">
+        <is>
+          <t>13(3)</t>
+        </is>
+      </c>
+      <c r="B16" s="22" t="inlineStr">
+        <is>
+          <t>Restore to accrual only when all arrears are paid</t>
+        </is>
+      </c>
+      <c r="C16" s="22" t="inlineStr">
+        <is>
+          <t>Restore a facility to accrual only when the borrower has paid all past-due principal and interest.</t>
+        </is>
+      </c>
+      <c r="D16" s="23" t="inlineStr">
+        <is>
+          <t>Outstanding</t>
+        </is>
+      </c>
+      <c r="E16" s="22" t="inlineStr">
+        <is>
+          <t>Not built: the Return reclassifies each period from the day count alone, so a facility leaves the non-performing classes as soon as its days overdue fall below the band, whether or not all arrears are paid. The IFRS 9 cure period (stage_cure_months) holds the stage, not the RBM accrual status.</t>
+        </is>
+      </c>
+      <c r="F16" s="22" t="inlineStr"/>
+      <c r="G16" s="22" t="inlineStr">
+        <is>
+          <t>Outstanding (Dupleix): hold a non-performing facility on non-accrual until its arrears are nil.</t>
+        </is>
+      </c>
+      <c r="H16" s="22" t="inlineStr">
+        <is>
+          <t>Reports: RBM Return (provisional) /rbm-return</t>
+        </is>
+      </c>
+      <c r="I16" s="22" t="inlineStr"/>
+      <c r="J16" s="22" t="inlineStr">
+        <is>
+          <t>stage_cure_months (IFRS 9 stage only)</t>
+        </is>
+      </c>
+      <c r="K16" s="22" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="22" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>14 and Schedule</t>
         </is>
       </c>
       <c r="B17" s="22" t="inlineStr">
         <is>
-          <t>Returns to the Reserve Bank</t>
+          <t>Minimum provisions by class</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
         <is>
-          <t>Submit the classification and provisioning return in the prescribed form and frequency.</t>
+          <t>Provide at least 0 percent on standard, 5 on special mention, 20 on substandard, 50 on doubtful and 100 on loss.</t>
         </is>
       </c>
       <c r="D17" s="23" t="inlineStr">
@@ -1535,43 +1882,392 @@
       </c>
       <c r="E17" s="22" t="inlineStr">
         <is>
-          <t>RbmReturnService fills the return in the directive's own order from the system: A the facilities by class and term under the directive's day bands, B the minimum provision per class against the IFRS 9 allowance with the higher of the two, C interest in suspense on non-performing facilities, D restructured facilities (awaiting the Reschedule Report), E the security on the register; on the screen with the CSV. The layout is provisional: the prescribed form is MAIIC Risk's and is not in the repository.</t>
-        </is>
-      </c>
-      <c r="F17" s="22" t="inlineStr"/>
+          <t>The RBM Return (section B) and the RBM Classification report apply the five rates to the gross carrying amount. The Provision Comparison report applies the same rates to EAD (carrying amount plus undrawn commitments; Ifrs9ReportsController::provisionComparison), so two screens give different minimums for one month. An unused helper (Ifrs9ReportsController::rbmRate) still holds wrong rates (1, 1, 50 percent). The directive says nothing of netting security; the Return does not net it.</t>
+        </is>
+      </c>
+      <c r="F17" s="22" t="inlineStr">
+        <is>
+          <t>Until 14 October 2026 this row was keyed '12' and said 'net of eligible security', which is not in the Gazette.</t>
+        </is>
+      </c>
       <c r="G17" s="22" t="inlineStr">
         <is>
-          <t>Partially done: every line is filled; the form's own order and wording are applied when Risk supplies it.</t>
+          <t>Partially done: the rates are right on the Return; the Provision Comparison must use the same base.</t>
         </is>
       </c>
       <c r="H17" s="22" t="inlineStr">
         <is>
-          <t>Risk &amp; Regulatory, RBM Return (provisional): /rbm-return; Risk &amp; Regulatory, RBM Classification: /ifrs9-reports/rbm-classification; IFRS 9 vs RBM: /ifrs9-reports/ifrs9-vs-rbm</t>
+          <t>Reports: RBM Return (provisional) /rbm-return (section B); Reports: RBM Classification /ifrs9-reports/rbm-classification; IFRS 9 vs RBM /ifrs9-reports/ifrs9-vs-rbm; Reports: Provision Comparison /ifrs9-reports/provision-comparison</t>
         </is>
       </c>
       <c r="I17" s="22" t="inlineStr"/>
-      <c r="J17" s="22" t="inlineStr">
+      <c r="J17" s="22" t="inlineStr"/>
+      <c r="K17" s="22" t="inlineStr">
+        <is>
+          <t>Tests\Feature\Rbm\RbmReturnServiceTest::test_the_return_fills_the_sections_from_the_book</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="22" t="inlineStr">
+        <is>
+          <t>15(1)</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>Excess of the regulatory provision over IFRS to a loan loss reserve</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="inlineStr">
+        <is>
+          <t>Where the directive's provisions exceed the IFRS impairment, the excess is an appropriation of retained earnings to a loan loss reserve.</t>
+        </is>
+      </c>
+      <c r="D18" s="23" t="inlineStr">
+        <is>
+          <t>Partially done</t>
+        </is>
+      </c>
+      <c r="E18" s="22" t="inlineStr">
+        <is>
+          <t>Section B's totals set the minimum provision against the IFRS 9 allowance and show the higher of the two; there is no line labelled loan loss reserve. On the fresh bootstrap at September 2026 the minimum is about 3.62bn against an IFRS 9 allowance of 11.57bn (undiscounted), so the reserve is nil in total, although the loss class alone carries a 1.51bn minimum against 0.86bn of allowance.</t>
+        </is>
+      </c>
+      <c r="F18" s="22" t="inlineStr">
+        <is>
+          <t>Figures from the fresh bootstrap maiic_ifrs9_results2 (13 October 2026, before commit 216aee2), main book (the six MAIIC and FInES loan GLs) at September 2026.</t>
+        </is>
+      </c>
+      <c r="G18" s="22" t="inlineStr">
+        <is>
+          <t>Partially done: the comparison is there; the reserve line is not.</t>
+        </is>
+      </c>
+      <c r="H18" s="22" t="inlineStr">
+        <is>
+          <t>Reports: RBM Return (provisional) /rbm-return (section B totals)</t>
+        </is>
+      </c>
+      <c r="I18" s="22" t="inlineStr"/>
+      <c r="J18" s="22" t="inlineStr"/>
+      <c r="K18" s="22" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="22" t="inlineStr">
+        <is>
+          <t>15(2), 15(4)</t>
+        </is>
+      </c>
+      <c r="B19" s="22" t="inlineStr">
+        <is>
+          <t>The reserve is not capital; released only after recoveries or with the Registrar's approval</t>
+        </is>
+      </c>
+      <c r="C19" s="22" t="inlineStr">
+        <is>
+          <t>The loan loss reserve is not capital where no longer available for unidentified losses; it is credited back to retained earnings only after recoveries or with the Registrar's prior approval.</t>
+        </is>
+      </c>
+      <c r="D19" s="23" t="inlineStr">
+        <is>
+          <t>Not applicable, documented</t>
+        </is>
+      </c>
+      <c r="E19" s="22" t="inlineStr">
+        <is>
+          <t>An accounting and capital treatment in MAIIC's books, outside the ECL and EIR system.</t>
+        </is>
+      </c>
+      <c r="F19" s="22" t="inlineStr">
+        <is>
+          <t>Finance applies it when it posts the reserve.</t>
+        </is>
+      </c>
+      <c r="G19" s="22" t="inlineStr">
+        <is>
+          <t>Not applicable, documented: Finance's posting, not a system output.</t>
+        </is>
+      </c>
+      <c r="H19" s="22" t="inlineStr"/>
+      <c r="I19" s="22" t="inlineStr"/>
+      <c r="J19" s="22" t="inlineStr"/>
+      <c r="K19" s="22" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="22" t="inlineStr">
+        <is>
+          <t>15(3)</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="inlineStr">
+        <is>
+          <t>Report loan loss reserves on the call report as prescribed</t>
+        </is>
+      </c>
+      <c r="C20" s="22" t="inlineStr">
+        <is>
+          <t>Report loan loss reserves separately on the call report in the form the Registrar prescribes.</t>
+        </is>
+      </c>
+      <c r="D20" s="23" t="inlineStr">
+        <is>
+          <t>Partially done</t>
+        </is>
+      </c>
+      <c r="E20" s="22" t="inlineStr">
+        <is>
+          <t>RbmReturnService fills a provisional return (A classification by class and term, B minimum provision against the IFRS 9 allowance, C interest in suspense, D restructured facilities, E security held) on the screen and as CSV, Excel and PDF. The prescribed call report form is not in the repository, the reserve is not a line of its own, section D is empty, and the section headings on the screen and the download cite the wrong paragraphs (RbmReturnController: 'sections 9 to 11', 'section 12', 'section 15', 'section 17'; they should be 10, 14 and 15, 16(1) and 15(3)).</t>
+        </is>
+      </c>
+      <c r="F20" s="22" t="inlineStr">
+        <is>
+          <t>Until 14 October 2026 this row was keyed '17', which is the monetary penalties paragraph.</t>
+        </is>
+      </c>
+      <c r="G20" s="22" t="inlineStr">
+        <is>
+          <t>Partially done: the lines are filled; the prescribed form, the reserve line and the citations are owed.</t>
+        </is>
+      </c>
+      <c r="H20" s="22" t="inlineStr">
+        <is>
+          <t>Reports: RBM Return (provisional) /rbm-return</t>
+        </is>
+      </c>
+      <c r="I20" s="22" t="inlineStr"/>
+      <c r="J20" s="22" t="inlineStr">
         <is>
           <t>dpd_basis</t>
         </is>
       </c>
-      <c r="K17" s="22" t="inlineStr">
-        <is>
-          <t>Tests\Feature\Rbm\RbmReturnServiceTest</t>
-        </is>
-      </c>
+      <c r="K20" s="22" t="inlineStr">
+        <is>
+          <t>Tests\Feature\Rbm\RbmReturnServiceTest::test_the_return_fills_the_sections_from_the_book</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="22" t="inlineStr">
+        <is>
+          <t>16(1)</t>
+        </is>
+      </c>
+      <c r="B21" s="22" t="inlineStr">
+        <is>
+          <t>No restructure, renegotiation, roll-over or modification without Board approval</t>
+        </is>
+      </c>
+      <c r="C21" s="22" t="inlineStr">
+        <is>
+          <t>An institution shall not restructure, renegotiate, roll over or modify the terms of a credit facility unless approved by the Board.</t>
+        </is>
+      </c>
+      <c r="D21" s="23" t="inlineStr">
+        <is>
+          <t>Outstanding</t>
+        </is>
+      </c>
+      <c r="E21" s="22" t="inlineStr">
+        <is>
+          <t>Not built: there is no restructure register and no record of Board approval. E-Banker's reschedule history (RS_02a to RS_02g, landed 12 October 2026; 46,230 RS_02a rows on the fresh bootstrap) is read only to find the instalment chart in force for staging (InstalmentChartHistory); section D of the Return is null (RbmReturnService: 'awaited from the vendor', which is stale).</t>
+        </is>
+      </c>
+      <c r="F21" s="22" t="inlineStr">
+        <is>
+          <t>Until 14 October 2026 this row was keyed '15' and waited on the vendor; the data has arrived and the register is Dupleix's build.</t>
+        </is>
+      </c>
+      <c r="G21" s="22" t="inlineStr">
+        <is>
+          <t>Outstanding (Dupleix): a restructure register from RS_02 with the Board approval reference, feeding section D.</t>
+        </is>
+      </c>
+      <c r="H21" s="22" t="inlineStr">
+        <is>
+          <t>Reports: RBM Return (provisional) /rbm-return (section D); Imports &amp; Feeds, E-Banker Loads: /eir-feed</t>
+        </is>
+      </c>
+      <c r="I21" s="22" t="inlineStr"/>
+      <c r="J21" s="22" t="inlineStr">
+        <is>
+          <t>rate_change_classification (not read yet); modification_threshold (not read yet)</t>
+        </is>
+      </c>
+      <c r="K21" s="22" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="22" t="inlineStr">
+        <is>
+          <t>16(2)</t>
+        </is>
+      </c>
+      <c r="B22" s="22" t="inlineStr">
+        <is>
+          <t>Single borrower or group limit of 25 percent of core capital</t>
+        </is>
+      </c>
+      <c r="C22" s="22" t="inlineStr">
+        <is>
+          <t>Facilities to a single borrower or group of related borrowers shall not exceed 25 percent of core capital without the Registrar's prior approval.</t>
+        </is>
+      </c>
+      <c r="D22" s="23" t="inlineStr">
+        <is>
+          <t>Outstanding</t>
+        </is>
+      </c>
+      <c r="E22" s="22" t="inlineStr">
+        <is>
+          <t>Not built: core capital is not held in the system and borrowers are not grouped; the concentration report lists names over a typed amount only.</t>
+        </is>
+      </c>
+      <c r="F22" s="22" t="inlineStr"/>
+      <c r="G22" s="22" t="inlineStr">
+        <is>
+          <t>Outstanding: Finance supplies core capital each quarter; Dupleix adds the 25 percent test and the related-borrower grouping.</t>
+        </is>
+      </c>
+      <c r="H22" s="22" t="inlineStr">
+        <is>
+          <t>Reports: Concentration and large exposures /ifrs9-reports/concentration</t>
+        </is>
+      </c>
+      <c r="I22" s="22" t="inlineStr"/>
+      <c r="J22" s="22" t="inlineStr"/>
+      <c r="K22" s="22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="22" t="inlineStr">
+        <is>
+          <t>16(3)</t>
+        </is>
+      </c>
+      <c r="B23" s="22" t="inlineStr">
+        <is>
+          <t>No overdraft facilities</t>
+        </is>
+      </c>
+      <c r="C23" s="22" t="inlineStr">
+        <is>
+          <t>An institution shall not extend any overdraft credit facilities.</t>
+        </is>
+      </c>
+      <c r="D23" s="23" t="inlineStr">
+        <is>
+          <t>Not applicable, documented</t>
+        </is>
+      </c>
+      <c r="E23" s="22" t="inlineStr">
+        <is>
+          <t>A lending restriction; the in-scope loan GLs (1050101 to 1050103, 1050201, 1050202, 1050401) are term-loan GLs and the system holds no overdraft product.</t>
+        </is>
+      </c>
+      <c r="F23" s="22" t="inlineStr"/>
+      <c r="G23" s="22" t="inlineStr">
+        <is>
+          <t>Not applicable, documented: no overdraft product in the book.</t>
+        </is>
+      </c>
+      <c r="H23" s="22" t="inlineStr"/>
+      <c r="I23" s="22" t="inlineStr"/>
+      <c r="J23" s="22" t="inlineStr"/>
+      <c r="K23" s="22" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="22" t="inlineStr">
+        <is>
+          <t>3 to 9</t>
+        </is>
+      </c>
+      <c r="B24" s="22" t="inlineStr">
+        <is>
+          <t>Objectives; Board and executive duties; lending criteria; funding records; internal audit; independent risk function</t>
+        </is>
+      </c>
+      <c r="C24" s="22" t="inlineStr">
+        <is>
+          <t>Board approval of facilities and policies, an analytical framework, MIS, a credit bureau report before lending, records of undisbursed lines, yearly internal audit of the portfolio, an independent risk function.</t>
+        </is>
+      </c>
+      <c r="D24" s="23" t="inlineStr">
+        <is>
+          <t>Not applicable, documented</t>
+        </is>
+      </c>
+      <c r="E24" s="22" t="inlineStr">
+        <is>
+          <t>Governance and lending-process duties of MAIIC; the system supplies the classified book, the reports and the audit trail that support them.</t>
+        </is>
+      </c>
+      <c r="F24" s="22" t="inlineStr">
+        <is>
+          <t>Paragraphs 4(b)(vi), 4(b)(x) and 5(1)(b) are audited in their own rows.</t>
+        </is>
+      </c>
+      <c r="G24" s="22" t="inlineStr">
+        <is>
+          <t>Not applicable, documented: policy and process, outside the system.</t>
+        </is>
+      </c>
+      <c r="H24" s="22" t="inlineStr"/>
+      <c r="I24" s="22" t="inlineStr"/>
+      <c r="J24" s="22" t="inlineStr"/>
+      <c r="K24" s="22" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="15" t="inlineStr">
+        <is>
+          <t>PART IV - ENFORCEMENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="22" t="inlineStr">
+        <is>
+          <t>17, 18</t>
+        </is>
+      </c>
+      <c r="B26" s="22" t="inlineStr">
+        <is>
+          <t>Monetary and administrative penalties; auditor qualification</t>
+        </is>
+      </c>
+      <c r="C26" s="22" t="inlineStr">
+        <is>
+          <t>The Registrar may impose penalties; an institution that fails to comply has its financial statements qualified by the external auditor.</t>
+        </is>
+      </c>
+      <c r="D26" s="23" t="inlineStr">
+        <is>
+          <t>Not applicable, documented</t>
+        </is>
+      </c>
+      <c r="E26" s="22" t="inlineStr">
+        <is>
+          <t>Enforcement provisions; nothing for the system to do.</t>
+        </is>
+      </c>
+      <c r="F26" s="22" t="inlineStr"/>
+      <c r="G26" s="22" t="inlineStr">
+        <is>
+          <t>Not applicable, documented.</t>
+        </is>
+      </c>
+      <c r="H26" s="22" t="inlineStr"/>
+      <c r="I26" s="22" t="inlineStr"/>
+      <c r="J26" s="22" t="inlineStr"/>
+      <c r="K26" s="22" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:K17"/>
-  <mergeCells count="6">
+  <autoFilter ref="A4:K26"/>
+  <mergeCells count="4">
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A5:K5"/>
     <mergeCell ref="A7:K7"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A11:K11"/>
-    <mergeCell ref="A16:K16"/>
-    <mergeCell ref="A14:K14"/>
-    <mergeCell ref="A5:K5"/>
+    <mergeCell ref="A25:K25"/>
   </mergeCells>
-  <conditionalFormatting sqref="D5:D17">
+  <conditionalFormatting sqref="D5:D26">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$D5="Done"</formula>
     </cfRule>
@@ -1588,13 +2284,13 @@
       <formula>$D5="Evidence needed from MAIIC"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K5:K17">
+  <conditionalFormatting sqref="K5:K26">
     <cfRule type="expression" priority="6" dxfId="2">
       <formula>AND($D5="Done",$K5="")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="D5:D17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="D5:D26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Done,Partially done,Outstanding,Not applicable, documented,Evidence needed from MAIIC"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1613,7 +2309,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1690,32 +2386,32 @@
       </c>
       <c r="B5" s="24" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16(1)</t>
         </is>
       </c>
       <c r="C5" s="22" t="inlineStr">
         <is>
-          <t>The restructured-loan register is not in the system</t>
+          <t>No restructure register</t>
         </is>
       </c>
       <c r="D5" s="22" t="inlineStr">
         <is>
-          <t>The Reschedule Report and the register are awaited from the vendor; restructured facilities cannot keep their classification as section 15 requires.</t>
+          <t>E-Banker's reschedule history (RS_02a to RS_02g) landed on 12 October 2026 and is read only for the instalment chart in force; no register of restructures with their Board approval exists and section D of the Return is null. (Until 14 October 2026 this finding said Barry was to obtain the Reschedule Report; it has arrived.)</t>
         </is>
       </c>
       <c r="E5" s="22" t="inlineStr">
         <is>
-          <t>Classification of restructured facilities may be too favourable.</t>
+          <t>Restructured facilities cannot be reported or shown to have Board approval; IFRS 9 modification (5.4.3) waits on the same register.</t>
         </is>
       </c>
       <c r="F5" s="22" t="inlineStr">
         <is>
-          <t>Barry obtains the Reschedule Report; the register is loaded by the feed and the classification holds it.</t>
+          <t>Dupleix builds the register from RS_02 (candidates confirmed by Credit), records the Board approval reference and fills section D.</t>
         </is>
       </c>
       <c r="G5" s="22" t="inlineStr">
         <is>
-          <t>Barry Makumba</t>
+          <t>Dupleix / Credit</t>
         </is>
       </c>
       <c r="H5" s="22" t="inlineStr">
@@ -1732,27 +2428,27 @@
       </c>
       <c r="B6" s="24" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15(3)</t>
         </is>
       </c>
       <c r="C6" s="22" t="inlineStr">
         <is>
-          <t>The prescribed return form is not in the repository</t>
+          <t>The prescribed call report form is not in the repository</t>
         </is>
       </c>
       <c r="D6" s="22" t="inlineStr">
         <is>
-          <t>The provisional return fills every line the directive asks for, in the directive's order; the Reserve Bank's own form (its schedule number, order and wording) has not been supplied.</t>
+          <t>The provisional return fills every line in the directive's order; the Registrar's own form has not been supplied, the loan loss reserve has no line, and the headings cite wrong paragraphs (sections 9 to 11, 12, 15, 17).</t>
         </is>
       </c>
       <c r="E6" s="22" t="inlineStr">
         <is>
-          <t>The return is still transcribed into the Bank's form by hand.</t>
+          <t>The return is still transcribed by hand and its citations mislead.</t>
         </is>
       </c>
       <c r="F6" s="22" t="inlineStr">
         <is>
-          <t>MAIIC Risk supplies the current form (the Excel or PDF sent to the Bank); the provisional layout is re-ordered and re-worded to it line for line; the figures stay as they are.</t>
+          <t>MAIIC Risk supplies the current form; Dupleix re-orders and re-words the lines to it, adds the reserve line and corrects the citations to 10, 14, 13, 16(1) and 15(3).</t>
         </is>
       </c>
       <c r="G6" s="22" t="inlineStr">
@@ -1772,9 +2468,9 @@
           <t>F3</t>
         </is>
       </c>
-      <c r="B7" s="22" t="inlineStr">
-        <is>
-          <t>9 to 11</t>
+      <c r="B7" s="24" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
@@ -1784,12 +2480,12 @@
       </c>
       <c r="D7" s="22" t="inlineStr">
         <is>
-          <t>The older RBM Classification report classified every facility on one ladder (90, 180, 365 days) with 1 percent on pass and special mention. Resolved in two steps: on 9 October 2026 the report, the provision comparison and the arrears ageing were put on one rule with the RBM Return; the system audit of the same day then found that rule itself carried wrong medium- and long-term bands (30/180/360/720, from a note carried between sessions) and both were corrected to the Gazette's section 10: short-term 30/90/180/365, medium and long 90/180/365/746, with a test at every boundary on both terms.</t>
+          <t>The older report classified every facility on one ladder (90, 180, 365 days). On 9 October 2026 the report, the provision comparison and the arrears ageing were put on one rule with the RBM Return, and the medium- and long-term bands were corrected to the Gazette's paragraph 10 (90/180/365/746), with a test at every boundary on both terms.</t>
         </is>
       </c>
       <c r="E7" s="22" t="inlineStr">
         <is>
-          <t>None remaining: both screens classify by the Gazette's bands.</t>
+          <t>None remaining.</t>
         </is>
       </c>
       <c r="F7" s="22" t="inlineStr">
@@ -1805,19 +2501,192 @@
       <c r="H7" s="22" t="inlineStr">
         <is>
           <t>Closed</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="22" t="inlineStr">
+        <is>
+          <t>F4</t>
+        </is>
+      </c>
+      <c r="B8" s="24" t="inlineStr">
+        <is>
+          <t>12, 13(3)</t>
+        </is>
+      </c>
+      <c r="C8" s="22" t="inlineStr">
+        <is>
+          <t>Loss-age write-off and restoration to accrual are not built</t>
+        </is>
+      </c>
+      <c r="D8" s="22" t="inlineStr">
+        <is>
+          <t>No loss-since date exists, so the paragraph 12 write-off deadline cannot be shown (10 loss facilities of 1,511.0m at September 2026 on the fresh bootstrap); a facility returns to accrual when its days fall, not when its arrears are paid.</t>
+        </is>
+      </c>
+      <c r="E8" s="22" t="inlineStr">
+        <is>
+          <t>The Return can carry loss facilities past the deadline and restore accrual too early.</t>
+        </is>
+      </c>
+      <c r="F8" s="22" t="inlineStr">
+        <is>
+          <t>Dupleix adds the loss-since date with a due-for-write-off flag, and an arrears-nil condition before restoration.</t>
+        </is>
+      </c>
+      <c r="G8" s="22" t="inlineStr">
+        <is>
+          <t>Dupleix</t>
+        </is>
+      </c>
+      <c r="H8" s="22" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="22" t="inlineStr">
+        <is>
+          <t>F5</t>
+        </is>
+      </c>
+      <c r="B9" s="24" t="inlineStr">
+        <is>
+          <t>13(1)</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t>Interest in suspense is not the directive's measure</t>
+        </is>
+      </c>
+      <c r="D9" s="22" t="inlineStr">
+        <is>
+          <t>Section C is one period's posted contractual interest less EIR interest; GL 1320 is not read and nothing is on the cash basis.</t>
+        </is>
+      </c>
+      <c r="E9" s="22" t="inlineStr">
+        <is>
+          <t>The suspense figure on the Return does not tie to the ledger.</t>
+        </is>
+      </c>
+      <c r="F9" s="22" t="inlineStr">
+        <is>
+          <t>Compute the cumulative uncollected interest on non-performing facilities on the cash basis and tie it to GL 1320.</t>
+        </is>
+      </c>
+      <c r="G9" s="22" t="inlineStr">
+        <is>
+          <t>Dupleix / Finance</t>
+        </is>
+      </c>
+      <c r="H9" s="22" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="22" t="inlineStr">
+        <is>
+          <t>F6</t>
+        </is>
+      </c>
+      <c r="B10" s="24" t="inlineStr">
+        <is>
+          <t>11(3), 16(2)</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="inlineStr">
+        <is>
+          <t>Large exposures and the 25 percent limit need core capital</t>
+        </is>
+      </c>
+      <c r="D10" s="22" t="inlineStr">
+        <is>
+          <t>The concentration report uses a typed threshold; core capital and related-borrower groups are not held.</t>
+        </is>
+      </c>
+      <c r="E10" s="22" t="inlineStr">
+        <is>
+          <t>The 10 percent large-exposure review and the 25 percent limit cannot be shown.</t>
+        </is>
+      </c>
+      <c r="F10" s="22" t="inlineStr">
+        <is>
+          <t>Finance supplies core capital quarterly; Dupleix adds the two tests and borrower grouping.</t>
+        </is>
+      </c>
+      <c r="G10" s="22" t="inlineStr">
+        <is>
+          <t>Finance / Dupleix</t>
+        </is>
+      </c>
+      <c r="H10" s="22" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="22" t="inlineStr">
+        <is>
+          <t>F7</t>
+        </is>
+      </c>
+      <c r="B11" s="24" t="inlineStr">
+        <is>
+          <t>14 and Schedule</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="inlineStr">
+        <is>
+          <t>Two bases for the minimum provision</t>
+        </is>
+      </c>
+      <c r="D11" s="22" t="inlineStr">
+        <is>
+          <t>The Return applies the rates to the gross carrying amount, the Provision Comparison report to EAD; an unused helper holds wrong rates.</t>
+        </is>
+      </c>
+      <c r="E11" s="22" t="inlineStr">
+        <is>
+          <t>Two screens disagree for one month.</t>
+        </is>
+      </c>
+      <c r="F11" s="22" t="inlineStr">
+        <is>
+          <t>Put the Provision Comparison on the gross carrying amount and delete the unused helper.</t>
+        </is>
+      </c>
+      <c r="G11" s="22" t="inlineStr">
+        <is>
+          <t>Dupleix</t>
+        </is>
+      </c>
+      <c r="H11" s="22" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="H5:H7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H5:H11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Open,In progress,Closed,Deferred"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
     <hyperlink ref="A2" location="'Contents'!A1" display="Back to Contents"/>
-    <hyperlink ref="B5" location="'Audit'!A15" display="15"/>
-    <hyperlink ref="B6" location="'Audit'!A17" display="17"/>
+    <hyperlink ref="B5" location="'Audit'!A21" display="16(1)"/>
+    <hyperlink ref="B6" location="'Audit'!A20" display="15(3)"/>
+    <hyperlink ref="B7" location="'Audit'!A10" display="10"/>
+    <hyperlink ref="B8" location="'Audit'!A13" display="12, 13(3)"/>
+    <hyperlink ref="B9" location="'Audit'!A14" display="13(1)"/>
+    <hyperlink ref="B10" location="'Audit'!A12" display="11(3), 16(2)"/>
+    <hyperlink ref="B11" location="'Audit'!A17" display="14 and Schedule"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -1831,7 +2700,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="64" customWidth="1" min="1" max="1"/>
@@ -1859,7 +2728,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-09 00:03:49 from maiic_ifrs9_bootstrap. The PASS/FAIL in column E is a formula on columns B and C, so it recomputes if a figure is typed over.</t>
+          <t>Generated 2026-10-14 08:30:44 from maiic_ifrs9_results2. The PASS/FAIL in column E is a formula on columns B and C, so it recomputes if a figure is typed over.</t>
         </is>
       </c>
     </row>
@@ -1919,7 +2788,7 @@
     <row r="6">
       <c r="A6" s="22" t="inlineStr">
         <is>
-          <t>Derived carrying amount against the stored report (over 2 cents)</t>
+          <t>Derived carrying amount against the stored report, in-scope loan GLs (over 2 cents)</t>
         </is>
       </c>
       <c r="B6" s="22" t="inlineStr">
@@ -1929,7 +2798,7 @@
       </c>
       <c r="C6" s="22" t="inlineStr">
         <is>
-          <t>0 of 2361 account-months</t>
+          <t>0 of 2495 account-months</t>
         </is>
       </c>
       <c r="D6" s="22" t="n">
@@ -1944,20 +2813,24 @@
     <row r="7">
       <c r="A7" s="22" t="inlineStr">
         <is>
-          <t>Year-end interest batch contra on 4215</t>
-        </is>
-      </c>
-      <c r="B7" s="25" t="n">
-        <v>32956675.55</v>
-      </c>
-      <c r="C7" s="25" t="n">
-        <v>32956675.55</v>
+          <t>Mega Farm: account-months whose MF_03 ledger differs from the Loan Book Report (reported, not a test)</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>77540 account-months</t>
+        </is>
       </c>
       <c r="D7" s="22" t="n">
-        <v>1</v>
+        <v>0.01</v>
       </c>
       <c r="E7" s="26">
-        <f>IF(ABS(B7-C7)&lt;=D7,"PASS","FAIL")</f>
+        <f>IF(B7=C7,"PASS","FAIL")</f>
         <v/>
       </c>
       <c r="F7" s="22" t="inlineStr"/>
@@ -1965,17 +2838,17 @@
     <row r="8">
       <c r="A8" s="22" t="inlineStr">
         <is>
-          <t>Year-end interest batch contra on 4216</t>
+          <t>Year-end interest batch contra on 4215</t>
         </is>
       </c>
       <c r="B8" s="25" t="n">
-        <v>-21733262.7</v>
+        <v>32956675.55</v>
       </c>
       <c r="C8" s="25" t="n">
-        <v>-21733262.7</v>
+        <v>32956675.55</v>
       </c>
       <c r="D8" s="22" t="n">
-        <v>0.01</v>
+        <v>1</v>
       </c>
       <c r="E8" s="26">
         <f>IF(ABS(B8-C8)&lt;=D8,"PASS","FAIL")</f>
@@ -1986,17 +2859,17 @@
     <row r="9">
       <c r="A9" s="22" t="inlineStr">
         <is>
-          <t>Loan book 1050101 at 31 Dec 2025 against the trial balance</t>
+          <t>Year-end interest batch contra on 4216</t>
         </is>
       </c>
       <c r="B9" s="25" t="n">
-        <v>1368737810.68</v>
+        <v>-21733262.7</v>
       </c>
       <c r="C9" s="25" t="n">
-        <v>1368737810.68</v>
+        <v>-21733262.7</v>
       </c>
       <c r="D9" s="22" t="n">
-        <v>1</v>
+        <v>0.01</v>
       </c>
       <c r="E9" s="26">
         <f>IF(ABS(B9-C9)&lt;=D9,"PASS","FAIL")</f>
@@ -2007,14 +2880,14 @@
     <row r="10">
       <c r="A10" s="22" t="inlineStr">
         <is>
-          <t>Loan book 1050102 at 31 Dec 2025 against the trial balance</t>
+          <t>Loan book 1050101 at 31 Dec 2025 against the trial balance</t>
         </is>
       </c>
       <c r="B10" s="25" t="n">
-        <v>6434045052.56</v>
+        <v>1368737810.68</v>
       </c>
       <c r="C10" s="25" t="n">
-        <v>6434045052.56</v>
+        <v>1368737810.68</v>
       </c>
       <c r="D10" s="22" t="n">
         <v>1</v>
@@ -2028,14 +2901,14 @@
     <row r="11">
       <c r="A11" s="22" t="inlineStr">
         <is>
-          <t>Loan book 1050201 at 31 Dec 2025 against the trial balance (accepted exception, spec 3.5: -400,000.00)</t>
+          <t>Loan book 1050102 at 31 Dec 2025 against the trial balance</t>
         </is>
       </c>
       <c r="B11" s="25" t="n">
-        <v>1402393139.46</v>
+        <v>6434045052.56</v>
       </c>
       <c r="C11" s="25" t="n">
-        <v>1401993139.46</v>
+        <v>6434045052.56</v>
       </c>
       <c r="D11" s="22" t="n">
         <v>1</v>
@@ -2049,14 +2922,14 @@
     <row r="12">
       <c r="A12" s="22" t="inlineStr">
         <is>
-          <t>Loan book 1050202 at 31 Dec 2025 against the trial balance (accepted exception, spec 3.5: 1,000,000.00)</t>
+          <t>Loan book 1050201 at 31 Dec 2025 against the trial balance (accepted exception, spec 3.5: -400,000.00)</t>
         </is>
       </c>
       <c r="B12" s="25" t="n">
-        <v>3808288656.15</v>
+        <v>1402393139.46</v>
       </c>
       <c r="C12" s="25" t="n">
-        <v>3809288656.15</v>
+        <v>1401993139.46</v>
       </c>
       <c r="D12" s="22" t="n">
         <v>1</v>
@@ -2070,14 +2943,14 @@
     <row r="13">
       <c r="A13" s="22" t="inlineStr">
         <is>
-          <t>Loan book 1050401 at 31 Dec 2025 against the trial balance</t>
+          <t>Loan book 1050202 at 31 Dec 2025 against the trial balance (accepted exception, spec 3.5: 1,000,000.00)</t>
         </is>
       </c>
       <c r="B13" s="25" t="n">
-        <v>1827148120.69</v>
+        <v>3808288656.15</v>
       </c>
       <c r="C13" s="25" t="n">
-        <v>1827148120.69</v>
+        <v>3809288656.15</v>
       </c>
       <c r="D13" s="22" t="n">
         <v>1</v>
@@ -2088,8 +2961,29 @@
       </c>
       <c r="F13" s="22" t="inlineStr"/>
     </row>
+    <row r="14">
+      <c r="A14" s="22" t="inlineStr">
+        <is>
+          <t>Loan book 1050401 at 31 Dec 2025 against the trial balance</t>
+        </is>
+      </c>
+      <c r="B14" s="25" t="n">
+        <v>1827148120.69</v>
+      </c>
+      <c r="C14" s="25" t="n">
+        <v>1827148120.69</v>
+      </c>
+      <c r="D14" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" s="26">
+        <f>IF(ABS(B14-C14)&lt;=D14,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F14" s="22" t="inlineStr"/>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="E5:E13">
+  <conditionalFormatting sqref="E5:E14">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$E5="PASS"</formula>
     </cfRule>

--- a/docs/compliance/RBM_DFI_Directive_2018_Compliance_Audit.xlsx
+++ b/docs/compliance/RBM_DFI_Directive_2018_Compliance_Audit.xlsx
@@ -1697,32 +1697,36 @@
       </c>
       <c r="D13" s="23" t="inlineStr">
         <is>
-          <t>Outstanding</t>
+          <t>Partially done</t>
         </is>
       </c>
       <c r="E13" s="22" t="inlineStr">
         <is>
-          <t>Not built: nothing records when a facility first became loss, so the age of a loss classification is unknown and no facility is flagged as due for write-off. The write-off register is not linked to the RBM Return. On the fresh bootstrap at September 2026, 10 medium- and long-term facilities of 1,511.0m are in the loss class.</t>
+          <t>Built 14 October 2026: the RBM Return's section 'Loss facilities to be written off' lists each loss facility with the month it became loss on the loan books (the unbroken run of loss classification by days past due and term; 'at or before' where the run reaches the first month held), its age in months, the quarter-end by which it must be written off and its status (overdue, due this quarter, due next quarter). On the fresh bootstrap at September 2026: 10 facilities of 1,510,956,083.45, 7 of them (1,030,047,803.06) past the write-off quarter. The write-off itself is a person's act in the write-off register; the system shows the deadline, it does not write off.</t>
         </is>
       </c>
       <c r="F13" s="22" t="inlineStr">
         <is>
-          <t>Figures from the fresh bootstrap maiic_ifrs9_results2 (13 October 2026, before commit 216aee2), main book (the six MAIIC and FInES loan GLs) at September 2026.</t>
+          <t>Figures from the fresh bootstrap maiic_ifrs9_results2 (13 October 2026, before commit 216aee2), main book (the six MAIIC and FInES loan GLs) at September 2026. Until 14 October 2026 this row was Outstanding.</t>
         </is>
       </c>
       <c r="G13" s="22" t="inlineStr">
         <is>
-          <t>Outstanding (Dupleix): a loss-since date and a due-for-write-off flag on the Return.</t>
+          <t>Partially done: the list and the deadline are built; the overdue facilities are for Credit and Finance to write off (or explain) in the register.</t>
         </is>
       </c>
       <c r="H13" s="22" t="inlineStr">
         <is>
-          <t>Reports: RBM Return (provisional) /rbm-return; /eir-write-offs</t>
+          <t>Reports: RBM Return (provisional) /rbm-return (Loss facilities to be written off); /eir-write-offs</t>
         </is>
       </c>
       <c r="I13" s="22" t="inlineStr"/>
       <c r="J13" s="22" t="inlineStr"/>
-      <c r="K13" s="22" t="inlineStr"/>
+      <c r="K13" s="22" t="inlineStr">
+        <is>
+          <t>Tests\Feature\Rbm\RbmReturnServiceTest::test_loss_facilities_are_listed_with_the_quarter_they_must_be_written_off_by</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="22" t="inlineStr">
@@ -1747,13 +1751,17 @@
       </c>
       <c r="E14" s="22" t="inlineStr">
         <is>
-          <t>Section C of the RBM Return reports, for the non-performing facilities, one period's contractual interest posted by E-Banker less the EIR interest recognised on the net basis. That is not the directive's measure: it is not cumulative, it is not on the cash basis (interest received), and GL 1320 (interest in suspense) is read nowhere. Under IFRS 9 the EIR engine recognises Stage 3 interest on the net carrying amount (5.4.1(b)), which is not the directive's cash basis either.</t>
-        </is>
-      </c>
-      <c r="F14" s="22" t="inlineStr"/>
+          <t>Section C of the RBM Return reports the month's contractual interest posted less the EIR interest on the net basis and, since 14 October 2026, the cumulative measure: the contractual interest charged on each facility non-performing at the month-end since the month it became non-performing on the loan books, with the cash received in the same window beside it and GL 1320 from the trial balance as the tie (with the difference). At September 2026 on the fresh bootstrap: 821,916,269.33 charged since non-performing on 50 facilities, 760,304,079.21 received; the trial balances from March 2026 carry no 1320 line (the last held is 21,865,867.35 credit at February 2026, unchanged since January 2025, so E-Banker posts no suspense). Not measured: the part of the cash received that is interest, because the ledger does not split a repayment, so the cash-basis income the directive allows is shown as a named gap.</t>
+        </is>
+      </c>
+      <c r="F14" s="22" t="inlineStr">
+        <is>
+          <t>Until 14 October 2026 section C was one period's figure only and GL 1320 was read nowhere.</t>
+        </is>
+      </c>
       <c r="G14" s="22" t="inlineStr">
         <is>
-          <t>Partially done: the gap between the posted and the recognised interest is shown; the directive's suspense balance is not computed or tied to GL 1320.</t>
+          <t>Partially done: the cumulative suspense and the GL 1320 tie are built; the cash-basis split and Finance's posting of suspense are open.</t>
         </is>
       </c>
       <c r="H14" s="22" t="inlineStr">
@@ -1767,7 +1775,11 @@
           <t>stage3_interest_basis</t>
         </is>
       </c>
-      <c r="K14" s="22" t="inlineStr"/>
+      <c r="K14" s="22" t="inlineStr">
+        <is>
+          <t>Tests\Feature\Rbm\RbmReturnServiceTest::test_cumulative_interest_in_suspense_is_measured_and_tied_to_gl_1320</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="22" t="inlineStr">
@@ -1877,22 +1889,22 @@
       </c>
       <c r="D17" s="23" t="inlineStr">
         <is>
-          <t>Partially done</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
         <is>
-          <t>The RBM Return (section B) and the RBM Classification report apply the five rates to the gross carrying amount. The Provision Comparison report applies the same rates to EAD (carrying amount plus undrawn commitments; Ifrs9ReportsController::provisionComparison), so two screens give different minimums for one month. An unused helper (Ifrs9ReportsController::rbmRate) still holds wrong rates (1, 1, 50 percent). The directive says nothing of netting security; the Return does not net it.</t>
+          <t>The RBM Return (section B), the RBM Classification report and, since 14 October 2026, the Provision Comparison report apply the five rates to the gross carrying amount (the Provision Comparison had used EAD); the unused helper with wrong rates (Ifrs9ReportsController::rbmRate) is deleted. The IFRS 9 allowance set against the minimum is the booked (discounted) allowance, with any loan that has no discounted figure counted and named. The directive says nothing of netting security; the Return does not net it.</t>
         </is>
       </c>
       <c r="F17" s="22" t="inlineStr">
         <is>
-          <t>Until 14 October 2026 this row was keyed '12' and said 'net of eligible security', which is not in the Gazette.</t>
+          <t>Until 14 October 2026 this row was keyed '12' and said 'net of eligible security', which is not in the Gazette; and it was Partially done (two bases).</t>
         </is>
       </c>
       <c r="G17" s="22" t="inlineStr">
         <is>
-          <t>Partially done: the rates are right on the Return; the Provision Comparison must use the same base.</t>
+          <t>Compliant.</t>
         </is>
       </c>
       <c r="H17" s="22" t="inlineStr">
@@ -1931,17 +1943,17 @@
       </c>
       <c r="E18" s="22" t="inlineStr">
         <is>
-          <t>Section B's totals set the minimum provision against the IFRS 9 allowance and show the higher of the two; there is no line labelled loan loss reserve. On the fresh bootstrap at September 2026 the minimum is about 3.62bn against an IFRS 9 allowance of 11.57bn (undiscounted), so the reserve is nil in total, although the loss class alone carries a 1.51bn minimum against 0.86bn of allowance.</t>
+          <t>Section B's totals set the minimum provision against the IFRS 9 allowance, show the higher of the two and, since 14 October 2026, a line labelled loan loss reserve (paragraph 15(1)): the minimum over the allowance. On the fresh bootstrap at September 2026 the minimum is 3,618,045,560.09 against an IFRS 9 allowance of 11,579,201,589.52 (booked; 38 loans at their undiscounted ECL of 4,460,558,036.40 because they have no discounted figure), so the reserve is nil in total, although the loss class alone carries a 1.51bn minimum against 0.89bn of allowance. The reserve is computed in total, as the paragraph reads.</t>
         </is>
       </c>
       <c r="F18" s="22" t="inlineStr">
         <is>
-          <t>Figures from the fresh bootstrap maiic_ifrs9_results2 (13 October 2026, before commit 216aee2), main book (the six MAIIC and FInES loan GLs) at September 2026.</t>
+          <t>Figures from the fresh bootstrap maiic_ifrs9_results2 (13 October 2026, before commit 216aee2), main book (the six MAIIC and FInES loan GLs) at September 2026. Until 14 October 2026 there was no reserve line.</t>
         </is>
       </c>
       <c r="G18" s="22" t="inlineStr">
         <is>
-          <t>Partially done: the comparison is there; the reserve line is not.</t>
+          <t>Partially done: the reserve line is built; the appropriation is a Finance entry, and the allowance it rests on is not wholly discounted yet.</t>
         </is>
       </c>
       <c r="H18" s="22" t="inlineStr">
@@ -1951,7 +1963,11 @@
       </c>
       <c r="I18" s="22" t="inlineStr"/>
       <c r="J18" s="22" t="inlineStr"/>
-      <c r="K18" s="22" t="inlineStr"/>
+      <c r="K18" s="22" t="inlineStr">
+        <is>
+          <t>Tests\Feature\Rbm\RbmReturnServiceTest::test_the_allowance_is_the_booked_discounted_allowance_and_a_gap_is_named</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="22" t="inlineStr">
@@ -2017,7 +2033,7 @@
       </c>
       <c r="E20" s="22" t="inlineStr">
         <is>
-          <t>RbmReturnService fills a provisional return (A classification by class and term, B minimum provision against the IFRS 9 allowance, C interest in suspense, D restructured facilities, E security held) on the screen and as CSV, Excel and PDF. The prescribed call report form is not in the repository, the reserve is not a line of its own, section D is empty, and the section headings on the screen and the download cite the wrong paragraphs (RbmReturnController: 'sections 9 to 11', 'section 12', 'section 15', 'section 17'; they should be 10, 14 and 15, 16(1) and 15(3)).</t>
+          <t>RbmReturnService fills a provisional return (A classification by class and term, B minimum provision against the IFRS 9 allowance, C interest in suspense, D restructured facilities, E security held) on the screen and as CSV, Excel and PDF. The prescribed call report form is not in the repository, the reserve is not a line of its own, section D lists only restructures confirmed on the register (none yet), and the section headings on the screen and the download cite the wrong paragraphs (RbmReturnController: 'sections 9 to 11', 'section 12', 'section 15', 'section 17'; they should be 10, 14 and 15, 16(1) and 15(3)).</t>
         </is>
       </c>
       <c r="F20" s="22" t="inlineStr">
@@ -2065,36 +2081,40 @@
       </c>
       <c r="D21" s="23" t="inlineStr">
         <is>
-          <t>Outstanding</t>
+          <t>Partially done</t>
         </is>
       </c>
       <c r="E21" s="22" t="inlineStr">
         <is>
-          <t>Not built: there is no restructure register and no record of Board approval. E-Banker's reschedule history (RS_02a to RS_02g, landed 12 October 2026; 46,230 RS_02a rows on the fresh bootstrap) is read only to find the instalment chart in force for staging (InstalmentChartHistory); section D of the Return is null (RbmReturnService: 'awaited from the vendor', which is stale).</t>
+          <t>The restructure register (EIR Data, Restructures &amp; Resets) holds the candidates the detector finds in E-Banker's reschedule history (RS_02a to RS_02f), the migration worksheet and the rate moves of fixed-rate loans; the bootstrap and the month-end run the detector only, and a candidate becomes a restructure only when one person classifies it with a reason and Board approval reference and another approves. Section D of the Return lists every facility with a confirmed restructure by the month-end with its Board approval, counts those restructured in the month and those without a Board approval recorded (flagged in red), and counts the candidates awaiting confirmation without reporting them; on the screen and in the CSV, Excel and PDF. On the scratch clone maiic_ifrs9_wire of 14 October 2026 (a copy of the restructure build's database, migrated): 70 candidates and 323 rate moves recorded, none confirmed, so section D lists no facility and says so.</t>
         </is>
       </c>
       <c r="F21" s="22" t="inlineStr">
         <is>
-          <t>Until 14 October 2026 this row was keyed '15' and waited on the vendor; the data has arrived and the register is Dupleix's build.</t>
+          <t>Until 14 October 2026 this row was Outstanding: no register existed and section D was null.</t>
         </is>
       </c>
       <c r="G21" s="22" t="inlineStr">
         <is>
-          <t>Outstanding (Dupleix): a restructure register from RS_02 with the Board approval reference, feeding section D.</t>
+          <t>Partially done: built; Credit classifies the candidates and MAIIC records the Board approval of each restructure it confirms.</t>
         </is>
       </c>
       <c r="H21" s="22" t="inlineStr">
         <is>
-          <t>Reports: RBM Return (provisional) /rbm-return (section D); Imports &amp; Feeds, E-Banker Loads: /eir-feed</t>
+          <t>Reports: RBM Return (provisional) /rbm-return (section D); EIR Data, Restructures &amp; Resets: /eir-restructures</t>
         </is>
       </c>
       <c r="I21" s="22" t="inlineStr"/>
       <c r="J21" s="22" t="inlineStr">
         <is>
-          <t>rate_change_classification (not read yet); modification_threshold (not read yet)</t>
-        </is>
-      </c>
-      <c r="K21" s="22" t="inlineStr"/>
+          <t>rate_change_classification; modification_threshold</t>
+        </is>
+      </c>
+      <c r="K21" s="22" t="inlineStr">
+        <is>
+          <t>Tests\Feature\Rbm\RbmReturnServiceTest::test_section_d_lists_the_confirmed_restructures_with_their_board_approval; Tests\Feature\Eir\RestructureRegisterTest::test_the_rbm_section_d_reports_only_confirmed_restructures_and_names_a_missing_board_approval; Tests\Feature\Eir\RestructureDetectionWiringTest::test_the_detection_step_finds_and_never_confirms_and_the_bootstrap_line_counts_the_candidates</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="22" t="inlineStr">
@@ -2396,27 +2416,27 @@
       </c>
       <c r="D5" s="22" t="inlineStr">
         <is>
-          <t>E-Banker's reschedule history (RS_02a to RS_02g) landed on 12 October 2026 and is read only for the instalment chart in force; no register of restructures with their Board approval exists and section D of the Return is null. (Until 14 October 2026 this finding said Barry was to obtain the Reschedule Report; it has arrived.)</t>
+          <t>E-Banker's reschedule history (RS_02a to RS_02g) landed on 12 October 2026 and was read only for the instalment chart in force; no register of restructures with their Board approval existed and section D of the Return was null. Status 14 October 2026: built and wired (uncommitted in the working tree): the register with maker-checker and the Board approval reference, the detector in the bootstrap and the month-end (detection only), and section D listing the confirmed restructures with their Board approval. On the scratch clone 70 candidates await classification.</t>
         </is>
       </c>
       <c r="E5" s="22" t="inlineStr">
         <is>
-          <t>Restructured facilities cannot be reported or shown to have Board approval; IFRS 9 modification (5.4.3) waits on the same register.</t>
+          <t>Until the candidates are classified the Return reports no restructured facility.</t>
         </is>
       </c>
       <c r="F5" s="22" t="inlineStr">
         <is>
-          <t>Dupleix builds the register from RS_02 (candidates confirmed by Credit), records the Board approval reference and fills section D.</t>
+          <t>Credit classifies the candidates; MAIIC records the Board approval of each restructure it confirms.</t>
         </is>
       </c>
       <c r="G5" s="22" t="inlineStr">
         <is>
-          <t>Dupleix / Credit</t>
+          <t>Credit / MAIIC</t>
         </is>
       </c>
       <c r="H5" s="22" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>In progress</t>
         </is>
       </c>
     </row>
@@ -2438,17 +2458,17 @@
       </c>
       <c r="D6" s="22" t="inlineStr">
         <is>
-          <t>The provisional return fills every line in the directive's order; the Registrar's own form has not been supplied, the loan loss reserve has no line, and the headings cite wrong paragraphs (sections 9 to 11, 12, 15, 17).</t>
+          <t>The provisional return fills every line in the directive's order; the Registrar's own form has not been supplied, the loan loss reserve has no line, and the headings cite wrong paragraphs (sections 9 to 11, 12, 15, 17). Status 14 October 2026: the citations are corrected (10 and 11, 12, 13, 14 and the Schedule, 15, 16(1), 15(3)) and the reserve line added; the form is still awaited.</t>
         </is>
       </c>
       <c r="E6" s="22" t="inlineStr">
         <is>
-          <t>The return is still transcribed by hand and its citations mislead.</t>
+          <t>The return is still transcribed by hand.</t>
         </is>
       </c>
       <c r="F6" s="22" t="inlineStr">
         <is>
-          <t>MAIIC Risk supplies the current form; Dupleix re-orders and re-words the lines to it, adds the reserve line and corrects the citations to 10, 14, 13, 16(1) and 15(3).</t>
+          <t>MAIIC Risk supplies the current form; Dupleix re-orders and re-words the lines to it.</t>
         </is>
       </c>
       <c r="G6" s="22" t="inlineStr">
@@ -2522,27 +2542,27 @@
       </c>
       <c r="D8" s="22" t="inlineStr">
         <is>
-          <t>No loss-since date exists, so the paragraph 12 write-off deadline cannot be shown (10 loss facilities of 1,511.0m at September 2026 on the fresh bootstrap); a facility returns to accrual when its days fall, not when its arrears are paid.</t>
+          <t>No loss-since date exists, so the paragraph 12 write-off deadline cannot be shown (10 loss facilities of 1,511.0m at September 2026 on the fresh bootstrap); a facility returns to accrual when its days fall, not when its arrears are paid. Status 14 October 2026: paragraph 12 is built (loss since, age, write-off quarter, status; 7 of the 10 overdue); 13(3) is not.</t>
         </is>
       </c>
       <c r="E8" s="22" t="inlineStr">
         <is>
-          <t>The Return can carry loss facilities past the deadline and restore accrual too early.</t>
+          <t>The Return can restore accrual too early.</t>
         </is>
       </c>
       <c r="F8" s="22" t="inlineStr">
         <is>
-          <t>Dupleix adds the loss-since date with a due-for-write-off flag, and an arrears-nil condition before restoration.</t>
+          <t>Dupleix adds an arrears-nil condition before restoration; Credit and Finance act on the 7 overdue loss facilities.</t>
         </is>
       </c>
       <c r="G8" s="22" t="inlineStr">
         <is>
-          <t>Dupleix</t>
+          <t>Dupleix / Credit</t>
         </is>
       </c>
       <c r="H8" s="22" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>In progress</t>
         </is>
       </c>
     </row>
@@ -2564,27 +2584,27 @@
       </c>
       <c r="D9" s="22" t="inlineStr">
         <is>
-          <t>Section C is one period's posted contractual interest less EIR interest; GL 1320 is not read and nothing is on the cash basis.</t>
+          <t>Section C is one period's posted contractual interest less EIR interest; GL 1320 is not read and nothing is on the cash basis. Status 14 October 2026: the cumulative interest charged since each facility became non-performing is computed and set against GL 1320; the cash-basis split is a named gap and the trial balances carry no 1320 line from March 2026.</t>
         </is>
       </c>
       <c r="E9" s="22" t="inlineStr">
         <is>
-          <t>The suspense figure on the Return does not tie to the ledger.</t>
+          <t>The suspense on the Return does not yet tie to a posted suspense balance.</t>
         </is>
       </c>
       <c r="F9" s="22" t="inlineStr">
         <is>
-          <t>Compute the cumulative uncollected interest on non-performing facilities on the cash basis and tie it to GL 1320.</t>
+          <t>Finance posts (or confirms) interest suspense on GL 1320; the cash received is split between principal and interest (allocation rule from Finance) so the cash-basis income can be deducted.</t>
         </is>
       </c>
       <c r="G9" s="22" t="inlineStr">
         <is>
-          <t>Dupleix / Finance</t>
+          <t>Finance / Dupleix</t>
         </is>
       </c>
       <c r="H9" s="22" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>In progress</t>
         </is>
       </c>
     </row>
@@ -2648,17 +2668,17 @@
       </c>
       <c r="D11" s="22" t="inlineStr">
         <is>
-          <t>The Return applies the rates to the gross carrying amount, the Provision Comparison report to EAD; an unused helper holds wrong rates.</t>
+          <t>The Return applies the rates to the gross carrying amount, the Provision Comparison report to EAD; an unused helper holds wrong rates. Status 14 October 2026: done, both on the gross carrying amount; the helper is deleted.</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr">
         <is>
-          <t>Two screens disagree for one month.</t>
+          <t>None remaining.</t>
         </is>
       </c>
       <c r="F11" s="22" t="inlineStr">
         <is>
-          <t>Put the Provision Comparison on the gross carrying amount and delete the unused helper.</t>
+          <t>Done.</t>
         </is>
       </c>
       <c r="G11" s="22" t="inlineStr">
@@ -2668,7 +2688,7 @@
       </c>
       <c r="H11" s="22" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -2700,7 +2720,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="64" customWidth="1" min="1" max="1"/>
@@ -2728,7 +2748,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-14 08:30:44 from maiic_ifrs9_results2. The PASS/FAIL in column E is a formula on columns B and C, so it recomputes if a figure is typed over.</t>
+          <t>Generated 2026-10-14 10:44:41 from maiic_ifrs9_wire. The PASS/FAIL in column E is a formula on columns B and C, so it recomputes if a figure is typed over.</t>
         </is>
       </c>
     </row>
@@ -2982,8 +3002,1424 @@
       </c>
       <c r="F14" s="22" t="inlineStr"/>
     </row>
+    <row r="15">
+      <c r="A15" s="22" t="inlineStr">
+        <is>
+          <t>Pack inventory: ebanker-pack-2026-10-09: every file as committed and landed with its manifest rows and SHA-256; 13 received files not landed, each with its reason in the manifest</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="inlineStr">
+        <is>
+          <t>12 extracts, 111,513 rows</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t>12 extracts, 111,513 rows</t>
+        </is>
+      </c>
+      <c r="D15" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E15" s="26">
+        <f>IF(B15=C15,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F15" s="22" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="22" t="inlineStr">
+        <is>
+          <t>Pack inventory: ebanker-pack-2026-10-12: every file as committed and landed with its manifest rows and SHA-256; 2 received files not landed, each with its reason in the manifest</t>
+        </is>
+      </c>
+      <c r="B16" s="22" t="inlineStr">
+        <is>
+          <t>39 extracts, 511,785 rows</t>
+        </is>
+      </c>
+      <c r="C16" s="22" t="inlineStr">
+        <is>
+          <t>39 extracts, 511,785 rows</t>
+        </is>
+      </c>
+      <c r="D16" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E16" s="26">
+        <f>IF(B16=C16,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F16" s="22" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="22" t="inlineStr">
+        <is>
+          <t>Pack inventory: ebanker-pack-2026-10-12-p5: every file as committed and landed with its manifest rows and SHA-256; 1 received files not landed, each with its reason in the manifest</t>
+        </is>
+      </c>
+      <c r="B17" s="22" t="inlineStr">
+        <is>
+          <t>8 extracts, 470 rows</t>
+        </is>
+      </c>
+      <c r="C17" s="22" t="inlineStr">
+        <is>
+          <t>8 extracts, 470 rows</t>
+        </is>
+      </c>
+      <c r="D17" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E17" s="26">
+        <f>IF(B17=C17,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F17" s="22" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="22" t="inlineStr">
+        <is>
+          <t>Pack inventory: ebanker-pack-2026-10-12-p6: every file as committed and landed with its manifest rows and SHA-256; 0 received files not landed, each with its reason in the manifest</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>3 extracts, 236 rows</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="inlineStr">
+        <is>
+          <t>3 extracts, 236 rows</t>
+        </is>
+      </c>
+      <c r="D18" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E18" s="26">
+        <f>IF(B18=C18,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F18" s="22" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="22" t="inlineStr">
+        <is>
+          <t>Pack inventory: ebanker-pack-2026-10-13-p7: every file as committed and landed with its manifest rows and SHA-256; 0 received files not landed, each with its reason in the manifest</t>
+        </is>
+      </c>
+      <c r="B19" s="22" t="inlineStr">
+        <is>
+          <t>6 extracts, 32,244 rows</t>
+        </is>
+      </c>
+      <c r="C19" s="22" t="inlineStr">
+        <is>
+          <t>6 extracts, 32,244 rows</t>
+        </is>
+      </c>
+      <c r="D19" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E19" s="26">
+        <f>IF(B19=C19,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F19" s="22" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="22" t="inlineStr">
+        <is>
+          <t>Pack inventory: ebanker-pack-2026-10-13-p8: every file as committed and landed with its manifest rows and SHA-256; 6 received files not landed, each with its reason in the manifest</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="inlineStr">
+        <is>
+          <t>4 extracts, 103 rows</t>
+        </is>
+      </c>
+      <c r="C20" s="22" t="inlineStr">
+        <is>
+          <t>4 extracts, 103 rows</t>
+        </is>
+      </c>
+      <c r="D20" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E20" s="26">
+        <f>IF(B20=C20,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F20" s="22" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="22" t="inlineStr">
+        <is>
+          <t>Pack inventory: ebanker-pack-2026-10-14: every file as committed and landed with its manifest rows and SHA-256; 13 received files not landed, each with its reason in the manifest</t>
+        </is>
+      </c>
+      <c r="B21" s="22" t="inlineStr">
+        <is>
+          <t>2 extracts, 426 rows</t>
+        </is>
+      </c>
+      <c r="C21" s="22" t="inlineStr">
+        <is>
+          <t>2 extracts, 426 rows</t>
+        </is>
+      </c>
+      <c r="D21" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E21" s="26">
+        <f>IF(B21=C21,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F21" s="22" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="22" t="inlineStr">
+        <is>
+          <t>Pack inventory: manifest.json (packs 1 and 2, data dictionary, trial balances, take-on): every file as committed and landed with its manifest rows and SHA-256; 3 received files not landed, each with its reason in the manifest; 30 workbooks and scripts, 23 landed by the bootstrap</t>
+        </is>
+      </c>
+      <c r="B22" s="22" t="inlineStr">
+        <is>
+          <t>54 extracts, 85,174 rows, 23 workbooks</t>
+        </is>
+      </c>
+      <c r="C22" s="22" t="inlineStr">
+        <is>
+          <t>54 extracts, 85,174 rows, 23 workbooks</t>
+        </is>
+      </c>
+      <c r="D22" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E22" s="26">
+        <f>IF(B22=C22,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F22" s="22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="22" t="inlineStr">
+        <is>
+          <t>Take-on worksheet (CV_10) against the take-on postings of 31 Jul 2024: term loans on the worksheet with take-on postings</t>
+        </is>
+      </c>
+      <c r="B23" s="25" t="n">
+        <v>77</v>
+      </c>
+      <c r="C23" s="25" t="n">
+        <v>77</v>
+      </c>
+      <c r="D23" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E23" s="26">
+        <f>IF(ABS(B23-C23)&lt;=D23,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F23" s="22" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="22" t="inlineStr">
+        <is>
+          <t>Take-on worksheet (CV_10) against the take-on postings of 31 Jul 2024: loans whose principal taken on (301) = NEWDISBURS_AMT, to the cent</t>
+        </is>
+      </c>
+      <c r="B24" s="25" t="n">
+        <v>76</v>
+      </c>
+      <c r="C24" s="25" t="n">
+        <v>76</v>
+      </c>
+      <c r="D24" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E24" s="26">
+        <f>IF(ABS(B24-C24)&lt;=D24,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F24" s="22" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="22" t="inlineStr">
+        <is>
+          <t>Take-on worksheet (CV_10) against the take-on postings of 31 Jul 2024: loans whose opening interest (303) = TOTAL_INT_CHARG, to the cent</t>
+        </is>
+      </c>
+      <c r="B25" s="25" t="n">
+        <v>76</v>
+      </c>
+      <c r="C25" s="25" t="n">
+        <v>76</v>
+      </c>
+      <c r="D25" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E25" s="26">
+        <f>IF(ABS(B25-C25)&lt;=D25,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F25" s="22" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="22" t="inlineStr">
+        <is>
+          <t>Take-on worksheet (CV_10) against the take-on postings of 31 Jul 2024: loans whose opening recoveries (305) = TOTA_REPAY_UPTO, to the cent</t>
+        </is>
+      </c>
+      <c r="B26" s="25" t="n">
+        <v>72</v>
+      </c>
+      <c r="C26" s="25" t="n">
+        <v>72</v>
+      </c>
+      <c r="D26" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E26" s="26">
+        <f>IF(ABS(B26-C26)&lt;=D26,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F26" s="22" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="22" t="inlineStr">
+        <is>
+          <t>Ledger copy CUMVOUCH_BK240824 (CV_04a) to 31 Dec 2023 against the GL opening balances of 1 Jan 2024 (CV_14), 4 loan GLs: sum of the differences</t>
+        </is>
+      </c>
+      <c r="B27" s="25" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C27" s="25" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D27" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E27" s="26">
+        <f>IF(ABS(B27-C27)&lt;=D27,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F27" s="22" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="22" t="inlineStr">
+        <is>
+          <t>Loan book 2025-12, MAIIC's loan GLs: carrying amount</t>
+        </is>
+      </c>
+      <c r="B28" s="22" t="inlineStr">
+        <is>
+          <t>no golden value committed (book_2025-12_maiic_amount)</t>
+        </is>
+      </c>
+      <c r="C28" s="25" t="n">
+        <v>14841212779.54</v>
+      </c>
+      <c r="D28" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E28" s="26">
+        <f>IF(B28=C28,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F28" s="22" t="inlineStr">
+        <is>
+          <t>the bootstrap's verify reports this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="22" t="inlineStr">
+        <is>
+          <t>Loan book 2025-12, MAIIC's loan GLs: rows</t>
+        </is>
+      </c>
+      <c r="B29" s="22" t="inlineStr">
+        <is>
+          <t>no golden value committed (book_2025-12_maiic_loans)</t>
+        </is>
+      </c>
+      <c r="C29" s="25" t="n">
+        <v>123</v>
+      </c>
+      <c r="D29" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E29" s="26">
+        <f>IF(B29=C29,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F29" s="22" t="inlineStr">
+        <is>
+          <t>the bootstrap's verify reports this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="22" t="inlineStr">
+        <is>
+          <t>Loan book 2025-12, Mega Farm programme GLs: carrying amount</t>
+        </is>
+      </c>
+      <c r="B30" s="22" t="inlineStr">
+        <is>
+          <t>no golden value committed (book_2025-12_megafarm_amount)</t>
+        </is>
+      </c>
+      <c r="C30" s="25" t="n">
+        <v>54498560819.6</v>
+      </c>
+      <c r="D30" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E30" s="26">
+        <f>IF(B30=C30,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F30" s="22" t="inlineStr">
+        <is>
+          <t>the bootstrap's verify reports this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="22" t="inlineStr">
+        <is>
+          <t>Loan book 2025-12, Mega Farm programme GLs: accounts with a balance</t>
+        </is>
+      </c>
+      <c r="B31" s="22" t="inlineStr">
+        <is>
+          <t>no golden value committed (book_2025-12_megafarm_accounts)</t>
+        </is>
+      </c>
+      <c r="C31" s="25" t="n">
+        <v>3671</v>
+      </c>
+      <c r="D31" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E31" s="26">
+        <f>IF(B31=C31,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F31" s="22" t="inlineStr">
+        <is>
+          <t>the bootstrap's verify reports this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="22" t="inlineStr">
+        <is>
+          <t>Loan book 2026-09, MAIIC's loan GLs: carrying amount</t>
+        </is>
+      </c>
+      <c r="B32" s="22" t="inlineStr">
+        <is>
+          <t>no golden value committed (book_2026-09_maiic_amount)</t>
+        </is>
+      </c>
+      <c r="C32" s="25" t="n">
+        <v>23189580235.43</v>
+      </c>
+      <c r="D32" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E32" s="26">
+        <f>IF(B32=C32,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F32" s="22" t="inlineStr">
+        <is>
+          <t>the bootstrap's verify reports this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="22" t="inlineStr">
+        <is>
+          <t>Loan book 2026-09, MAIIC's loan GLs: rows</t>
+        </is>
+      </c>
+      <c r="B33" s="22" t="inlineStr">
+        <is>
+          <t>no golden value committed (book_2026-09_maiic_loans)</t>
+        </is>
+      </c>
+      <c r="C33" s="25" t="n">
+        <v>134</v>
+      </c>
+      <c r="D33" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E33" s="26">
+        <f>IF(B33=C33,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F33" s="22" t="inlineStr">
+        <is>
+          <t>the bootstrap's verify reports this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="22" t="inlineStr">
+        <is>
+          <t>Loan book 2026-09, Mega Farm programme GLs: carrying amount</t>
+        </is>
+      </c>
+      <c r="B34" s="22" t="inlineStr">
+        <is>
+          <t>no golden value committed (book_2026-09_megafarm_amount)</t>
+        </is>
+      </c>
+      <c r="C34" s="25" t="n">
+        <v>56180761113.43</v>
+      </c>
+      <c r="D34" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E34" s="26">
+        <f>IF(B34=C34,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F34" s="22" t="inlineStr">
+        <is>
+          <t>the bootstrap's verify reports this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="22" t="inlineStr">
+        <is>
+          <t>Loan book 2026-09, Mega Farm programme GLs: accounts with a balance</t>
+        </is>
+      </c>
+      <c r="B35" s="22" t="inlineStr">
+        <is>
+          <t>no golden value committed (book_2026-09_megafarm_accounts)</t>
+        </is>
+      </c>
+      <c r="C35" s="25" t="n">
+        <v>3618</v>
+      </c>
+      <c r="D35" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E35" s="26">
+        <f>IF(B35=C35,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F35" s="22" t="inlineStr">
+        <is>
+          <t>the bootstrap's verify reports this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="22" t="inlineStr">
+        <is>
+          <t>Ledger write-offs on MAIIC loans (WriteOffClassifier): postings</t>
+        </is>
+      </c>
+      <c r="B36" s="22" t="inlineStr">
+        <is>
+          <t>no golden value committed (ledger_writeoffs_postings)</t>
+        </is>
+      </c>
+      <c r="C36" s="25" t="n">
+        <v>22</v>
+      </c>
+      <c r="D36" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E36" s="26">
+        <f>IF(B36=C36,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F36" s="22" t="inlineStr">
+        <is>
+          <t>the bootstrap's verify reports this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="22" t="inlineStr">
+        <is>
+          <t>Ledger write-offs on MAIIC loans (WriteOffClassifier): amount</t>
+        </is>
+      </c>
+      <c r="B37" s="22" t="inlineStr">
+        <is>
+          <t>no golden value committed (ledger_writeoffs_amount)</t>
+        </is>
+      </c>
+      <c r="C37" s="25" t="n">
+        <v>60778466.86</v>
+      </c>
+      <c r="D37" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E37" s="26">
+        <f>IF(B37=C37,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F37" s="22" t="inlineStr">
+        <is>
+          <t>the bootstrap's verify reports this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="22" t="inlineStr">
+        <is>
+          <t>ECL 2025-12, MAIIC's book: undiscounted</t>
+        </is>
+      </c>
+      <c r="B38" s="22" t="inlineStr">
+        <is>
+          <t>no golden value committed (ecl_2025-12_maiic_undiscounted)</t>
+        </is>
+      </c>
+      <c r="C38" s="25" t="n">
+        <v>3955543846.37</v>
+      </c>
+      <c r="D38" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E38" s="26">
+        <f>IF(B38=C38,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F38" s="22" t="inlineStr">
+        <is>
+          <t>the bootstrap's verify reports this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="22" t="inlineStr">
+        <is>
+          <t>ECL 2025-12, MAIIC's book: discounted at the EIR (booked)</t>
+        </is>
+      </c>
+      <c r="B39" s="22" t="inlineStr">
+        <is>
+          <t>no golden value committed (ecl_2025-12_maiic_discounted)</t>
+        </is>
+      </c>
+      <c r="C39" s="25" t="n">
+        <v>2593174242.3</v>
+      </c>
+      <c r="D39" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E39" s="26">
+        <f>IF(B39=C39,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F39" s="22" t="inlineStr">
+        <is>
+          <t>the bootstrap's verify reports this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="22" t="inlineStr">
+        <is>
+          <t>ECL 2025-12, MAIIC's book: loans discounted at the EIR</t>
+        </is>
+      </c>
+      <c r="B40" s="22" t="inlineStr">
+        <is>
+          <t>no golden value committed (ecl_2025-12_maiic_discounted_loans)</t>
+        </is>
+      </c>
+      <c r="C40" s="25" t="n">
+        <v>56</v>
+      </c>
+      <c r="D40" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E40" s="26">
+        <f>IF(B40=C40,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F40" s="22" t="inlineStr">
+        <is>
+          <t>the bootstrap's verify reports this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="22" t="inlineStr">
+        <is>
+          <t>ECL 2025-12, MAIIC's book, stage 1: discounted</t>
+        </is>
+      </c>
+      <c r="B41" s="22" t="inlineStr">
+        <is>
+          <t>no golden value committed (ecl_2025-12_maiic_stage1_discounted)</t>
+        </is>
+      </c>
+      <c r="C41" s="25" t="n">
+        <v>61318291.61</v>
+      </c>
+      <c r="D41" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E41" s="26">
+        <f>IF(B41=C41,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F41" s="22" t="inlineStr">
+        <is>
+          <t>the bootstrap's verify reports this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="22" t="inlineStr">
+        <is>
+          <t>ECL 2025-12, MAIIC's book, stage 2: discounted</t>
+        </is>
+      </c>
+      <c r="B42" s="22" t="inlineStr">
+        <is>
+          <t>no golden value committed (ecl_2025-12_maiic_stage2_discounted)</t>
+        </is>
+      </c>
+      <c r="C42" s="25" t="n">
+        <v>315409106.41</v>
+      </c>
+      <c r="D42" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E42" s="26">
+        <f>IF(B42=C42,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F42" s="22" t="inlineStr">
+        <is>
+          <t>the bootstrap's verify reports this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="22" t="inlineStr">
+        <is>
+          <t>ECL 2025-12, MAIIC's book, stage 3: discounted</t>
+        </is>
+      </c>
+      <c r="B43" s="22" t="inlineStr">
+        <is>
+          <t>no golden value committed (ecl_2025-12_maiic_stage3_discounted)</t>
+        </is>
+      </c>
+      <c r="C43" s="25" t="n">
+        <v>2216446844.28</v>
+      </c>
+      <c r="D43" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E43" s="26">
+        <f>IF(B43=C43,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F43" s="22" t="inlineStr">
+        <is>
+          <t>the bootstrap's verify reports this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="22" t="inlineStr">
+        <is>
+          <t>ECL 2025-12, Mega Farm programme (latest run)</t>
+        </is>
+      </c>
+      <c r="B44" s="22" t="inlineStr">
+        <is>
+          <t>no golden value committed (ecl_2025-12_megafarm_programme)</t>
+        </is>
+      </c>
+      <c r="C44" s="22" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="D44" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E44" s="26">
+        <f>IF(B44=C44,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F44" s="22" t="inlineStr">
+        <is>
+          <t>the bootstrap's verify reports this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="22" t="inlineStr">
+        <is>
+          <t>ECL 2025-12, Mega Farm: MAIIC's share</t>
+        </is>
+      </c>
+      <c r="B45" s="22" t="inlineStr">
+        <is>
+          <t>no golden value committed (ecl_2025-12_megafarm_maiic_share)</t>
+        </is>
+      </c>
+      <c r="C45" s="22" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="D45" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E45" s="26">
+        <f>IF(B45=C45,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F45" s="22" t="inlineStr">
+        <is>
+          <t>the bootstrap's verify reports this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="22" t="inlineStr">
+        <is>
+          <t>ECL 2026-09, MAIIC's book: undiscounted</t>
+        </is>
+      </c>
+      <c r="B46" s="22" t="inlineStr">
+        <is>
+          <t>no golden value committed (ecl_2026-09_maiic_undiscounted)</t>
+        </is>
+      </c>
+      <c r="C46" s="25" t="n">
+        <v>11569458915.88</v>
+      </c>
+      <c r="D46" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E46" s="26">
+        <f>IF(B46=C46,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F46" s="22" t="inlineStr">
+        <is>
+          <t>the bootstrap's verify reports this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="22" t="inlineStr">
+        <is>
+          <t>ECL 2026-09, MAIIC's book: discounted at the EIR (booked)</t>
+        </is>
+      </c>
+      <c r="B47" s="22" t="inlineStr">
+        <is>
+          <t>no golden value committed (ecl_2026-09_maiic_discounted)</t>
+        </is>
+      </c>
+      <c r="C47" s="25" t="n">
+        <v>7118643553.12</v>
+      </c>
+      <c r="D47" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E47" s="26">
+        <f>IF(B47=C47,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F47" s="22" t="inlineStr">
+        <is>
+          <t>the bootstrap's verify reports this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="22" t="inlineStr">
+        <is>
+          <t>ECL 2026-09, MAIIC's book: loans discounted at the EIR</t>
+        </is>
+      </c>
+      <c r="B48" s="22" t="inlineStr">
+        <is>
+          <t>no golden value committed (ecl_2026-09_maiic_discounted_loans)</t>
+        </is>
+      </c>
+      <c r="C48" s="25" t="n">
+        <v>62</v>
+      </c>
+      <c r="D48" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E48" s="26">
+        <f>IF(B48=C48,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F48" s="22" t="inlineStr">
+        <is>
+          <t>the bootstrap's verify reports this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="22" t="inlineStr">
+        <is>
+          <t>ECL 2026-09, MAIIC's book, stage 1: discounted</t>
+        </is>
+      </c>
+      <c r="B49" s="22" t="inlineStr">
+        <is>
+          <t>no golden value committed (ecl_2026-09_maiic_stage1_discounted)</t>
+        </is>
+      </c>
+      <c r="C49" s="25" t="n">
+        <v>219546033.9</v>
+      </c>
+      <c r="D49" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E49" s="26">
+        <f>IF(B49=C49,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F49" s="22" t="inlineStr">
+        <is>
+          <t>the bootstrap's verify reports this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="22" t="inlineStr">
+        <is>
+          <t>ECL 2026-09, MAIIC's book, stage 2: discounted</t>
+        </is>
+      </c>
+      <c r="B50" s="22" t="inlineStr">
+        <is>
+          <t>no golden value committed (ecl_2026-09_maiic_stage2_discounted)</t>
+        </is>
+      </c>
+      <c r="C50" s="25" t="n">
+        <v>183786390.69</v>
+      </c>
+      <c r="D50" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E50" s="26">
+        <f>IF(B50=C50,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F50" s="22" t="inlineStr">
+        <is>
+          <t>the bootstrap's verify reports this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="22" t="inlineStr">
+        <is>
+          <t>ECL 2026-09, MAIIC's book, stage 3: discounted</t>
+        </is>
+      </c>
+      <c r="B51" s="22" t="inlineStr">
+        <is>
+          <t>no golden value committed (ecl_2026-09_maiic_stage3_discounted)</t>
+        </is>
+      </c>
+      <c r="C51" s="25" t="n">
+        <v>6715311128.53</v>
+      </c>
+      <c r="D51" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E51" s="26">
+        <f>IF(B51=C51,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F51" s="22" t="inlineStr">
+        <is>
+          <t>the bootstrap's verify reports this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="22" t="inlineStr">
+        <is>
+          <t>ECL 2026-09, Mega Farm programme (latest run)</t>
+        </is>
+      </c>
+      <c r="B52" s="22" t="inlineStr">
+        <is>
+          <t>no golden value committed (ecl_2026-09_megafarm_programme)</t>
+        </is>
+      </c>
+      <c r="C52" s="25" t="n">
+        <v>45782301503.37</v>
+      </c>
+      <c r="D52" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E52" s="26">
+        <f>IF(B52=C52,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F52" s="22" t="inlineStr">
+        <is>
+          <t>the bootstrap's verify reports this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="22" t="inlineStr">
+        <is>
+          <t>ECL 2026-09, Mega Farm: MAIIC's share</t>
+        </is>
+      </c>
+      <c r="B53" s="22" t="inlineStr">
+        <is>
+          <t>no golden value committed (ecl_2026-09_megafarm_maiic_share)</t>
+        </is>
+      </c>
+      <c r="C53" s="25" t="n">
+        <v>2289115075.17</v>
+      </c>
+      <c r="D53" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E53" s="26">
+        <f>IF(B53=C53,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F53" s="22" t="inlineStr">
+        <is>
+          <t>the bootstrap's verify reports this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="22" t="inlineStr">
+        <is>
+          <t>EIR contracts locked</t>
+        </is>
+      </c>
+      <c r="B54" s="22" t="inlineStr">
+        <is>
+          <t>no golden value committed (eir_contracts_locked)</t>
+        </is>
+      </c>
+      <c r="C54" s="25" t="n">
+        <v>14</v>
+      </c>
+      <c r="D54" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E54" s="26">
+        <f>IF(B54=C54,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F54" s="22" t="inlineStr">
+        <is>
+          <t>the bootstrap's verify reports this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="22" t="inlineStr">
+        <is>
+          <t>EIR contracts blocked</t>
+        </is>
+      </c>
+      <c r="B55" s="22" t="inlineStr">
+        <is>
+          <t>no golden value committed (eir_contracts_blocked)</t>
+        </is>
+      </c>
+      <c r="C55" s="25" t="n">
+        <v>33</v>
+      </c>
+      <c r="D55" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E55" s="26">
+        <f>IF(B55=C55,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F55" s="22" t="inlineStr">
+        <is>
+          <t>the bootstrap's verify reports this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="22" t="inlineStr">
+        <is>
+          <t>EIR contracts solved (an EIR computed)</t>
+        </is>
+      </c>
+      <c r="B56" s="22" t="inlineStr">
+        <is>
+          <t>no golden value committed (eir_contracts_solved)</t>
+        </is>
+      </c>
+      <c r="C56" s="25" t="n">
+        <v>14</v>
+      </c>
+      <c r="D56" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E56" s="26">
+        <f>IF(B56=C56,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F56" s="22" t="inlineStr">
+        <is>
+          <t>the bootstrap's verify reports this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="22" t="inlineStr">
+        <is>
+          <t>EIR contracts in the contract master</t>
+        </is>
+      </c>
+      <c r="B57" s="22" t="inlineStr">
+        <is>
+          <t>no golden value committed (eir_contracts)</t>
+        </is>
+      </c>
+      <c r="C57" s="25" t="n">
+        <v>144</v>
+      </c>
+      <c r="D57" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E57" s="26">
+        <f>IF(B57=C57,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F57" s="22" t="inlineStr">
+        <is>
+          <t>the bootstrap's verify reports this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="22" t="inlineStr">
+        <is>
+          <t>Revenue 2024: EIR interest recognised</t>
+        </is>
+      </c>
+      <c r="B58" s="22" t="inlineStr">
+        <is>
+          <t>no golden value committed (revenue_2024_eir_interest)</t>
+        </is>
+      </c>
+      <c r="C58" s="25" t="n">
+        <v>25532678.7</v>
+      </c>
+      <c r="D58" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E58" s="26">
+        <f>IF(B58=C58,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F58" s="22" t="inlineStr">
+        <is>
+          <t>the bootstrap's verify reports this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="22" t="inlineStr">
+        <is>
+          <t>Revenue 2024: cash received</t>
+        </is>
+      </c>
+      <c r="B59" s="22" t="inlineStr">
+        <is>
+          <t>no golden value committed (revenue_2024_cash_received)</t>
+        </is>
+      </c>
+      <c r="C59" s="25" t="n">
+        <v>34200000</v>
+      </c>
+      <c r="D59" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E59" s="26">
+        <f>IF(B59=C59,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F59" s="22" t="inlineStr">
+        <is>
+          <t>the bootstrap's verify reports this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="22" t="inlineStr">
+        <is>
+          <t>Revenue 2024: roll-forward rows</t>
+        </is>
+      </c>
+      <c r="B60" s="22" t="inlineStr">
+        <is>
+          <t>no golden value committed (revenue_2024_rows)</t>
+        </is>
+      </c>
+      <c r="C60" s="25" t="n">
+        <v>20</v>
+      </c>
+      <c r="D60" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E60" s="26">
+        <f>IF(B60=C60,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F60" s="22" t="inlineStr">
+        <is>
+          <t>the bootstrap's verify reports this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="22" t="inlineStr">
+        <is>
+          <t>Revenue 2025: EIR interest recognised</t>
+        </is>
+      </c>
+      <c r="B61" s="22" t="inlineStr">
+        <is>
+          <t>no golden value committed (revenue_2025_eir_interest)</t>
+        </is>
+      </c>
+      <c r="C61" s="25" t="n">
+        <v>663970866.88</v>
+      </c>
+      <c r="D61" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E61" s="26">
+        <f>IF(B61=C61,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F61" s="22" t="inlineStr">
+        <is>
+          <t>the bootstrap's verify reports this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="22" t="inlineStr">
+        <is>
+          <t>Revenue 2025: cash received</t>
+        </is>
+      </c>
+      <c r="B62" s="22" t="inlineStr">
+        <is>
+          <t>no golden value committed (revenue_2025_cash_received)</t>
+        </is>
+      </c>
+      <c r="C62" s="25" t="n">
+        <v>1158267060.2</v>
+      </c>
+      <c r="D62" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E62" s="26">
+        <f>IF(B62=C62,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F62" s="22" t="inlineStr">
+        <is>
+          <t>the bootstrap's verify reports this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="22" t="inlineStr">
+        <is>
+          <t>Revenue 2025: roll-forward rows</t>
+        </is>
+      </c>
+      <c r="B63" s="22" t="inlineStr">
+        <is>
+          <t>no golden value committed (revenue_2025_rows)</t>
+        </is>
+      </c>
+      <c r="C63" s="25" t="n">
+        <v>126</v>
+      </c>
+      <c r="D63" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E63" s="26">
+        <f>IF(B63=C63,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F63" s="22" t="inlineStr">
+        <is>
+          <t>the bootstrap's verify reports this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="22" t="inlineStr">
+        <is>
+          <t>Revenue 2026: EIR interest recognised</t>
+        </is>
+      </c>
+      <c r="B64" s="22" t="inlineStr">
+        <is>
+          <t>no golden value committed (revenue_2026_eir_interest)</t>
+        </is>
+      </c>
+      <c r="C64" s="25" t="n">
+        <v>544517024.26</v>
+      </c>
+      <c r="D64" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E64" s="26">
+        <f>IF(B64=C64,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F64" s="22" t="inlineStr">
+        <is>
+          <t>the bootstrap's verify reports this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="22" t="inlineStr">
+        <is>
+          <t>Revenue 2026: cash received</t>
+        </is>
+      </c>
+      <c r="B65" s="22" t="inlineStr">
+        <is>
+          <t>no golden value committed (revenue_2026_cash_received)</t>
+        </is>
+      </c>
+      <c r="C65" s="25" t="n">
+        <v>2381610987.63</v>
+      </c>
+      <c r="D65" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E65" s="26">
+        <f>IF(B65=C65,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F65" s="22" t="inlineStr">
+        <is>
+          <t>the bootstrap's verify reports this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="22" t="inlineStr">
+        <is>
+          <t>Revenue 2026: roll-forward rows</t>
+        </is>
+      </c>
+      <c r="B66" s="22" t="inlineStr">
+        <is>
+          <t>no golden value committed (revenue_2026_rows)</t>
+        </is>
+      </c>
+      <c r="C66" s="25" t="n">
+        <v>113</v>
+      </c>
+      <c r="D66" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E66" s="26">
+        <f>IF(B66=C66,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F66" s="22" t="inlineStr">
+        <is>
+          <t>the bootstrap's verify reports this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="22" t="inlineStr">
+        <is>
+          <t>RBM return 2026-09: facilities classified loss (paragraph 12 list)</t>
+        </is>
+      </c>
+      <c r="B67" s="22" t="inlineStr">
+        <is>
+          <t>no golden value committed (rbm_2026-09_loss_facilities)</t>
+        </is>
+      </c>
+      <c r="C67" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="D67" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E67" s="26">
+        <f>IF(B67=C67,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F67" s="22" t="inlineStr">
+        <is>
+          <t>the bootstrap's verify reports this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="22" t="inlineStr">
+        <is>
+          <t>RBM return 2026-09: balance of the loss list</t>
+        </is>
+      </c>
+      <c r="B68" s="22" t="inlineStr">
+        <is>
+          <t>no golden value committed (rbm_2026-09_loss_balance)</t>
+        </is>
+      </c>
+      <c r="C68" s="25" t="n">
+        <v>1510956083.45</v>
+      </c>
+      <c r="D68" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E68" s="26">
+        <f>IF(B68=C68,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F68" s="22" t="inlineStr">
+        <is>
+          <t>the bootstrap's verify reports this row</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="E5:E14">
+  <conditionalFormatting sqref="E5:E68">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$E5="PASS"</formula>
     </cfRule>
